--- a/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>DTEGY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>123903700</v>
+        <v>121834600</v>
       </c>
       <c r="E8" s="3">
-        <v>116756900</v>
+        <v>124257800</v>
       </c>
       <c r="F8" s="3">
-        <v>109583900</v>
+        <v>117090400</v>
       </c>
       <c r="G8" s="3">
-        <v>87376100</v>
+        <v>109897000</v>
       </c>
       <c r="H8" s="3">
-        <v>82086800</v>
+        <v>87625800</v>
       </c>
       <c r="I8" s="3">
-        <v>81317500</v>
+        <v>82321300</v>
       </c>
       <c r="J8" s="3">
+        <v>81549800</v>
+      </c>
+      <c r="K8" s="3">
         <v>79308100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>70667900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70747100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>71929900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>63869600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>68847500</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>54302100</v>
+        <v>48405200</v>
       </c>
       <c r="E9" s="3">
-        <v>50544700</v>
+        <v>54457200</v>
       </c>
       <c r="F9" s="3">
-        <v>45477800</v>
+        <v>50689100</v>
       </c>
       <c r="G9" s="3">
-        <v>37442300</v>
+        <v>45607700</v>
       </c>
       <c r="H9" s="3">
-        <v>38779000</v>
+        <v>37549200</v>
       </c>
       <c r="I9" s="3">
-        <v>38895100</v>
+        <v>38889800</v>
       </c>
       <c r="J9" s="3">
+        <v>39006200</v>
+      </c>
+      <c r="K9" s="3">
         <v>37957600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42848100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>43514400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43368200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>37613100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39774600</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>69601700</v>
+        <v>73429300</v>
       </c>
       <c r="E10" s="3">
-        <v>66212100</v>
+        <v>69800500</v>
       </c>
       <c r="F10" s="3">
-        <v>64106100</v>
+        <v>66401300</v>
       </c>
       <c r="G10" s="3">
-        <v>49933900</v>
+        <v>64289300</v>
       </c>
       <c r="H10" s="3">
-        <v>43307800</v>
+        <v>50076500</v>
       </c>
       <c r="I10" s="3">
-        <v>42422400</v>
+        <v>43431500</v>
       </c>
       <c r="J10" s="3">
+        <v>42543600</v>
+      </c>
+      <c r="K10" s="3">
         <v>41350400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>27819900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27232800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>28561700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26256500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>29072900</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,77 +960,83 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-554400</v>
+        <v>1230600</v>
       </c>
       <c r="E14" s="3">
-        <v>912500</v>
+        <v>-556000</v>
       </c>
       <c r="F14" s="3">
-        <v>192000</v>
+        <v>915100</v>
       </c>
       <c r="G14" s="3">
-        <v>797500</v>
+        <v>192600</v>
       </c>
       <c r="H14" s="3">
-        <v>1306300</v>
+        <v>799800</v>
       </c>
       <c r="I14" s="3">
-        <v>532700</v>
+        <v>1310100</v>
       </c>
       <c r="J14" s="3">
+        <v>534300</v>
+      </c>
+      <c r="K14" s="3">
         <v>732400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>151100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>134400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>978500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>24202100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3917000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>28938000</v>
+        <v>25846700</v>
       </c>
       <c r="E15" s="3">
-        <v>29509800</v>
+        <v>29020700</v>
       </c>
       <c r="F15" s="3">
-        <v>27158600</v>
+        <v>29594100</v>
       </c>
       <c r="G15" s="3">
-        <v>18738000</v>
+        <v>27236200</v>
       </c>
       <c r="H15" s="3">
-        <v>14228700</v>
+        <v>18791500</v>
       </c>
       <c r="I15" s="3">
-        <v>13486600</v>
+        <v>14269300</v>
       </c>
       <c r="J15" s="3">
+        <v>13525100</v>
+      </c>
+      <c r="K15" s="3">
         <v>13766500</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>107179600</v>
+        <v>99204300</v>
       </c>
       <c r="E17" s="3">
-        <v>103121700</v>
+        <v>107485800</v>
       </c>
       <c r="F17" s="3">
-        <v>95691600</v>
+        <v>103416300</v>
       </c>
       <c r="G17" s="3">
-        <v>77115300</v>
+        <v>95965000</v>
       </c>
       <c r="H17" s="3">
-        <v>73378600</v>
+        <v>77335600</v>
       </c>
       <c r="I17" s="3">
-        <v>71136900</v>
+        <v>73588200</v>
       </c>
       <c r="J17" s="3">
+        <v>71340200</v>
+      </c>
+      <c r="K17" s="3">
         <v>69365100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63493800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>62564600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>66032600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>68219800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>62290600</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>16724200</v>
+        <v>22630300</v>
       </c>
       <c r="E18" s="3">
-        <v>13635200</v>
+        <v>16772000</v>
       </c>
       <c r="F18" s="3">
-        <v>13892300</v>
+        <v>13674200</v>
       </c>
       <c r="G18" s="3">
-        <v>10260800</v>
+        <v>13932000</v>
       </c>
       <c r="H18" s="3">
-        <v>8708200</v>
+        <v>10290200</v>
       </c>
       <c r="I18" s="3">
-        <v>10180600</v>
+        <v>8733100</v>
       </c>
       <c r="J18" s="3">
+        <v>10209600</v>
+      </c>
+      <c r="K18" s="3">
         <v>9942900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7174200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>8182600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5897300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4350300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6556900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1347600</v>
+        <v>-2439500</v>
       </c>
       <c r="E20" s="3">
-        <v>95500</v>
+        <v>1351400</v>
       </c>
       <c r="F20" s="3">
-        <v>554400</v>
+        <v>95800</v>
       </c>
       <c r="G20" s="3">
-        <v>558800</v>
+        <v>556000</v>
       </c>
       <c r="H20" s="3">
-        <v>-845200</v>
+        <v>560400</v>
       </c>
       <c r="I20" s="3">
-        <v>-2031100</v>
+        <v>-847600</v>
       </c>
       <c r="J20" s="3">
+        <v>-2036900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2063700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>366500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-262000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-492800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-80200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>30500</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>46978500</v>
+        <v>46433600</v>
       </c>
       <c r="E21" s="3">
-        <v>43225300</v>
+        <v>48582500</v>
       </c>
       <c r="F21" s="3">
-        <v>41430500</v>
+        <v>43536200</v>
       </c>
       <c r="G21" s="3">
-        <v>29630900</v>
+        <v>41720400</v>
       </c>
       <c r="H21" s="3">
-        <v>22869500</v>
+        <v>29835100</v>
       </c>
       <c r="I21" s="3">
-        <v>23969400</v>
+        <v>23030200</v>
       </c>
       <c r="J21" s="3">
+        <v>24138400</v>
+      </c>
+      <c r="K21" s="3">
         <v>22391200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18913100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19887200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18394400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19715700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>23544100</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6161700</v>
+        <v>7168400</v>
       </c>
       <c r="E22" s="3">
-        <v>5454300</v>
+        <v>6179300</v>
       </c>
       <c r="F22" s="3">
-        <v>5032200</v>
+        <v>5469900</v>
       </c>
       <c r="G22" s="3">
-        <v>2942500</v>
+        <v>5046600</v>
       </c>
       <c r="H22" s="3">
-        <v>2272000</v>
+        <v>2950900</v>
       </c>
       <c r="I22" s="3">
-        <v>2730900</v>
+        <v>2278500</v>
       </c>
       <c r="J22" s="3">
+        <v>2738700</v>
+      </c>
+      <c r="K22" s="3">
         <v>2945800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2663300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3009100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2858900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2568200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3043700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11910000</v>
+        <v>13022400</v>
       </c>
       <c r="E23" s="3">
-        <v>8276400</v>
+        <v>11944100</v>
       </c>
       <c r="F23" s="3">
-        <v>9414500</v>
+        <v>8300000</v>
       </c>
       <c r="G23" s="3">
-        <v>7877100</v>
+        <v>9441400</v>
       </c>
       <c r="H23" s="3">
-        <v>5591000</v>
+        <v>7899600</v>
       </c>
       <c r="I23" s="3">
-        <v>5418500</v>
+        <v>5607000</v>
       </c>
       <c r="J23" s="3">
+        <v>5434000</v>
+      </c>
+      <c r="K23" s="3">
         <v>4933500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4877400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4911600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2545500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6998700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3543700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2101600</v>
+        <v>3995500</v>
       </c>
       <c r="E24" s="3">
-        <v>1879200</v>
+        <v>2107600</v>
       </c>
       <c r="F24" s="3">
-        <v>2093000</v>
+        <v>1884600</v>
       </c>
       <c r="G24" s="3">
-        <v>2162400</v>
+        <v>2098900</v>
       </c>
       <c r="H24" s="3">
-        <v>1979000</v>
+        <v>2168600</v>
       </c>
       <c r="I24" s="3">
-        <v>-605400</v>
+        <v>1984700</v>
       </c>
       <c r="J24" s="3">
+        <v>-607200</v>
+      </c>
+      <c r="K24" s="3">
         <v>1565700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1302500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1248800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1105300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1664600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2757300</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9808400</v>
+        <v>9026900</v>
       </c>
       <c r="E26" s="3">
-        <v>6397200</v>
+        <v>9836400</v>
       </c>
       <c r="F26" s="3">
-        <v>7321600</v>
+        <v>6415400</v>
       </c>
       <c r="G26" s="3">
-        <v>5714700</v>
+        <v>7342500</v>
       </c>
       <c r="H26" s="3">
-        <v>3612000</v>
+        <v>5731000</v>
       </c>
       <c r="I26" s="3">
-        <v>6023900</v>
+        <v>3622300</v>
       </c>
       <c r="J26" s="3">
+        <v>6041100</v>
+      </c>
+      <c r="K26" s="3">
         <v>3367800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3574800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3662800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1440200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5334100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>786500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8200400</v>
+        <v>4452500</v>
       </c>
       <c r="E27" s="3">
-        <v>4306400</v>
+        <v>8223900</v>
       </c>
       <c r="F27" s="3">
-        <v>4511400</v>
+        <v>4318700</v>
       </c>
       <c r="G27" s="3">
-        <v>4195700</v>
+        <v>4524300</v>
       </c>
       <c r="H27" s="3">
-        <v>2350100</v>
+        <v>4207700</v>
       </c>
       <c r="I27" s="3">
-        <v>3755200</v>
+        <v>2356800</v>
       </c>
       <c r="J27" s="3">
+        <v>3765900</v>
+      </c>
+      <c r="K27" s="3">
         <v>2902400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3321700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3301500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1112500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5877600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>653800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,20 +1580,23 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>480700</v>
+        <v>14902600</v>
       </c>
       <c r="E29" s="3">
-        <v>224600</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+        <v>482000</v>
+      </c>
+      <c r="F29" s="3">
+        <v>225200</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>8</v>
@@ -1550,8 +1610,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1347600</v>
+        <v>2439500</v>
       </c>
       <c r="E32" s="3">
-        <v>-95500</v>
+        <v>-1351400</v>
       </c>
       <c r="F32" s="3">
-        <v>-554400</v>
+        <v>-95800</v>
       </c>
       <c r="G32" s="3">
-        <v>-558800</v>
+        <v>-556000</v>
       </c>
       <c r="H32" s="3">
-        <v>845200</v>
+        <v>-560400</v>
       </c>
       <c r="I32" s="3">
-        <v>2031100</v>
+        <v>847600</v>
       </c>
       <c r="J32" s="3">
+        <v>2036900</v>
+      </c>
+      <c r="K32" s="3">
         <v>2063700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-366500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>262000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>492800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>80200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-30500</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8681100</v>
+        <v>19355100</v>
       </c>
       <c r="E33" s="3">
-        <v>4531000</v>
+        <v>8705900</v>
       </c>
       <c r="F33" s="3">
-        <v>4511400</v>
+        <v>4543900</v>
       </c>
       <c r="G33" s="3">
-        <v>4195700</v>
+        <v>4524300</v>
       </c>
       <c r="H33" s="3">
-        <v>2350100</v>
+        <v>4207700</v>
       </c>
       <c r="I33" s="3">
-        <v>3755200</v>
+        <v>2356800</v>
       </c>
       <c r="J33" s="3">
+        <v>3765900</v>
+      </c>
+      <c r="K33" s="3">
         <v>2902400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3321700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3301500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1112500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5877600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>653800</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8681100</v>
+        <v>19355100</v>
       </c>
       <c r="E35" s="3">
-        <v>4531000</v>
+        <v>8705900</v>
       </c>
       <c r="F35" s="3">
-        <v>4511400</v>
+        <v>4543900</v>
       </c>
       <c r="G35" s="3">
-        <v>4195700</v>
+        <v>4524300</v>
       </c>
       <c r="H35" s="3">
-        <v>2350100</v>
+        <v>4207700</v>
       </c>
       <c r="I35" s="3">
-        <v>3755200</v>
+        <v>2356800</v>
       </c>
       <c r="J35" s="3">
+        <v>3765900</v>
+      </c>
+      <c r="K35" s="3">
         <v>2902400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3321700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3301500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1112500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5877600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>653800</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>6257200</v>
+        <v>7914800</v>
       </c>
       <c r="E41" s="3">
-        <v>8264400</v>
+        <v>6275100</v>
       </c>
       <c r="F41" s="3">
-        <v>14038800</v>
+        <v>8288100</v>
       </c>
       <c r="G41" s="3">
-        <v>5851400</v>
+        <v>14078900</v>
       </c>
       <c r="H41" s="3">
-        <v>3991700</v>
+        <v>5868100</v>
       </c>
       <c r="I41" s="3">
-        <v>3593500</v>
+        <v>4003100</v>
       </c>
       <c r="J41" s="3">
+        <v>3603800</v>
+      </c>
+      <c r="K41" s="3">
         <v>8405500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7040500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8494200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9533700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4420500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4400600</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>103100</v>
+        <v>119700</v>
       </c>
       <c r="E42" s="3">
-        <v>100900</v>
+        <v>103400</v>
       </c>
       <c r="F42" s="3">
-        <v>100900</v>
+        <v>101200</v>
       </c>
       <c r="G42" s="3">
-        <v>31500</v>
+        <v>101200</v>
       </c>
       <c r="H42" s="3">
-        <v>13000</v>
+        <v>31600</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>13100</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>2200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2301400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5570900</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>26046500</v>
+        <v>25611700</v>
       </c>
       <c r="E43" s="3">
-        <v>23244000</v>
+        <v>26120900</v>
       </c>
       <c r="F43" s="3">
-        <v>20532500</v>
+        <v>23310400</v>
       </c>
       <c r="G43" s="3">
-        <v>17728900</v>
+        <v>20591200</v>
       </c>
       <c r="H43" s="3">
-        <v>16198000</v>
+        <v>17779600</v>
       </c>
       <c r="I43" s="3">
-        <v>14076800</v>
+        <v>16244200</v>
       </c>
       <c r="J43" s="3">
+        <v>14117000</v>
+      </c>
+      <c r="K43" s="3">
         <v>15932100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>12311900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>14870200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12149800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9036500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15544800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2863300</v>
+        <v>2632100</v>
       </c>
       <c r="E44" s="3">
-        <v>3097700</v>
+        <v>2871500</v>
       </c>
       <c r="F44" s="3">
-        <v>2924100</v>
+        <v>3106500</v>
       </c>
       <c r="G44" s="3">
-        <v>1701300</v>
+        <v>2932400</v>
       </c>
       <c r="H44" s="3">
-        <v>1942100</v>
+        <v>1706100</v>
       </c>
       <c r="I44" s="3">
-        <v>2153700</v>
+        <v>1947700</v>
       </c>
       <c r="J44" s="3">
+        <v>2159900</v>
+      </c>
+      <c r="K44" s="3">
         <v>1767500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1885400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1697000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1270400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1214400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2544800</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7201100</v>
+        <v>3288200</v>
       </c>
       <c r="E45" s="3">
-        <v>7389900</v>
+        <v>7221700</v>
       </c>
       <c r="F45" s="3">
-        <v>2866600</v>
+        <v>7411000</v>
       </c>
       <c r="G45" s="3">
-        <v>1474500</v>
+        <v>2874800</v>
       </c>
       <c r="H45" s="3">
-        <v>1584100</v>
+        <v>1478700</v>
       </c>
       <c r="I45" s="3">
-        <v>2301300</v>
+        <v>1588600</v>
       </c>
       <c r="J45" s="3">
+        <v>2307900</v>
+      </c>
+      <c r="K45" s="3">
         <v>2795000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11611600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8580000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3312300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1735900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2315900</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>42471200</v>
+        <v>39566600</v>
       </c>
       <c r="E46" s="3">
-        <v>42096900</v>
+        <v>42592600</v>
       </c>
       <c r="F46" s="3">
-        <v>40462900</v>
+        <v>42217200</v>
       </c>
       <c r="G46" s="3">
-        <v>26787600</v>
+        <v>40578500</v>
       </c>
       <c r="H46" s="3">
-        <v>23729000</v>
+        <v>26864100</v>
       </c>
       <c r="I46" s="3">
-        <v>22125300</v>
+        <v>23796700</v>
       </c>
       <c r="J46" s="3">
+        <v>22188500</v>
+      </c>
+      <c r="K46" s="3">
         <v>28902200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32853400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33644900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>26272100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16490900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18622500</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>6902800</v>
+        <v>9515400</v>
       </c>
       <c r="E47" s="3">
-        <v>6264800</v>
+        <v>6922500</v>
       </c>
       <c r="F47" s="3">
-        <v>7550500</v>
+        <v>6282700</v>
       </c>
       <c r="G47" s="3">
-        <v>4866200</v>
+        <v>7572100</v>
       </c>
       <c r="H47" s="3">
-        <v>2344700</v>
+        <v>4880100</v>
       </c>
       <c r="I47" s="3">
-        <v>6908200</v>
+        <v>2351400</v>
       </c>
       <c r="J47" s="3">
+        <v>6927900</v>
+      </c>
+      <c r="K47" s="3">
         <v>9342900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4442500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3275500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9006200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9472400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10527900</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>107910000</v>
+        <v>106490000</v>
       </c>
       <c r="E48" s="3">
-        <v>100414000</v>
+        <v>108218000</v>
       </c>
       <c r="F48" s="3">
-        <v>99035500</v>
+        <v>100700000</v>
       </c>
       <c r="G48" s="3">
-        <v>73287400</v>
+        <v>99318500</v>
       </c>
       <c r="H48" s="3">
-        <v>54934600</v>
+        <v>73496800</v>
       </c>
       <c r="I48" s="3">
-        <v>50862600</v>
+        <v>55091600</v>
       </c>
       <c r="J48" s="3">
+        <v>51008000</v>
+      </c>
+      <c r="K48" s="3">
         <v>50732400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>45565400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44730400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44770200</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>202972000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>152551000</v>
+        <v>147986000</v>
       </c>
       <c r="E49" s="3">
-        <v>143922000</v>
+        <v>152987000</v>
       </c>
       <c r="F49" s="3">
-        <v>128102000</v>
+        <v>144333000</v>
       </c>
       <c r="G49" s="3">
-        <v>73999200</v>
+        <v>128468000</v>
       </c>
       <c r="H49" s="3">
-        <v>70470800</v>
+        <v>74210600</v>
       </c>
       <c r="I49" s="3">
-        <v>68208500</v>
+        <v>70672100</v>
       </c>
       <c r="J49" s="3">
+        <v>68403400</v>
+      </c>
+      <c r="K49" s="3">
         <v>65749900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>58211100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58222000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>54985700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>75914600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>117761000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14135400</v>
+        <v>12322700</v>
       </c>
       <c r="E52" s="3">
-        <v>12868100</v>
+        <v>14175800</v>
       </c>
       <c r="F52" s="3">
-        <v>12284400</v>
+        <v>12904900</v>
       </c>
       <c r="G52" s="3">
-        <v>6238800</v>
+        <v>12319500</v>
       </c>
       <c r="H52" s="3">
-        <v>6252900</v>
+        <v>6256600</v>
       </c>
       <c r="I52" s="3">
-        <v>5242700</v>
+        <v>6270700</v>
       </c>
       <c r="J52" s="3">
+        <v>5257700</v>
+      </c>
+      <c r="K52" s="3">
         <v>6378700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5841000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6187500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6294400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7088700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9460900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>323970000</v>
+        <v>315881000</v>
       </c>
       <c r="E54" s="3">
-        <v>305565000</v>
+        <v>324896000</v>
       </c>
       <c r="F54" s="3">
-        <v>287435000</v>
+        <v>306438000</v>
       </c>
       <c r="G54" s="3">
-        <v>185179000</v>
+        <v>288256000</v>
       </c>
       <c r="H54" s="3">
-        <v>157732000</v>
+        <v>185708000</v>
       </c>
       <c r="I54" s="3">
-        <v>153347000</v>
+        <v>158183000</v>
       </c>
       <c r="J54" s="3">
+        <v>153786000</v>
+      </c>
+      <c r="K54" s="3">
         <v>161106000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>146914000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146060000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>141329000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>118520000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>143787000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12999400</v>
+        <v>11727500</v>
       </c>
       <c r="E57" s="3">
-        <v>11279700</v>
+        <v>13036500</v>
       </c>
       <c r="F57" s="3">
-        <v>10514700</v>
+        <v>11311900</v>
       </c>
       <c r="G57" s="3">
-        <v>10209900</v>
+        <v>10544800</v>
       </c>
       <c r="H57" s="3">
-        <v>11608400</v>
+        <v>10239000</v>
       </c>
       <c r="I57" s="3">
-        <v>11863400</v>
+        <v>11641600</v>
       </c>
       <c r="J57" s="3">
+        <v>11897300</v>
+      </c>
+      <c r="K57" s="3">
         <v>11271000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11266600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10874400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8649700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7043700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15077600</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>20424000</v>
+        <v>14571800</v>
       </c>
       <c r="E58" s="3">
-        <v>17074600</v>
+        <v>19395400</v>
       </c>
       <c r="F58" s="3">
-        <v>17481500</v>
+        <v>17123400</v>
       </c>
       <c r="G58" s="3">
-        <v>14119100</v>
+        <v>17531500</v>
       </c>
       <c r="H58" s="3">
-        <v>9349400</v>
+        <v>14159400</v>
       </c>
       <c r="I58" s="3">
-        <v>7542900</v>
+        <v>9376200</v>
       </c>
       <c r="J58" s="3">
+        <v>7564500</v>
+      </c>
+      <c r="K58" s="3">
         <v>12321300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12831500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9269900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7060000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8352500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>23990300</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15823600</v>
+        <v>12942900</v>
       </c>
       <c r="E59" s="3">
-        <v>13746900</v>
+        <v>16955900</v>
       </c>
       <c r="F59" s="3">
-        <v>12295200</v>
+        <v>13786200</v>
       </c>
       <c r="G59" s="3">
-        <v>11381600</v>
+        <v>12330300</v>
       </c>
       <c r="H59" s="3">
-        <v>10663400</v>
+        <v>11414200</v>
       </c>
       <c r="I59" s="3">
-        <v>10285800</v>
+        <v>10693800</v>
       </c>
       <c r="J59" s="3">
+        <v>10315200</v>
+      </c>
+      <c r="K59" s="3">
         <v>12349500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10147800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11694100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11200000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17387900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17246800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>49247100</v>
+        <v>39242300</v>
       </c>
       <c r="E60" s="3">
-        <v>42101300</v>
+        <v>49387800</v>
       </c>
       <c r="F60" s="3">
-        <v>40291500</v>
+        <v>42221500</v>
       </c>
       <c r="G60" s="3">
-        <v>35710600</v>
+        <v>40406600</v>
       </c>
       <c r="H60" s="3">
-        <v>31621200</v>
+        <v>35812600</v>
       </c>
       <c r="I60" s="3">
-        <v>29692100</v>
+        <v>31711600</v>
       </c>
       <c r="J60" s="3">
+        <v>29776900</v>
+      </c>
+      <c r="K60" s="3">
         <v>35941700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>34245800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31838400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26909700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25248500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28423800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>140334000</v>
+        <v>138657000</v>
       </c>
       <c r="E61" s="3">
-        <v>137069000</v>
+        <v>140735000</v>
       </c>
       <c r="F61" s="3">
-        <v>131441000</v>
+        <v>137461000</v>
       </c>
       <c r="G61" s="3">
-        <v>76004300</v>
+        <v>131817000</v>
       </c>
       <c r="H61" s="3">
-        <v>55304600</v>
+        <v>76221400</v>
       </c>
       <c r="I61" s="3">
-        <v>52427200</v>
+        <v>55462600</v>
       </c>
       <c r="J61" s="3">
+        <v>52577000</v>
+      </c>
+      <c r="K61" s="3">
         <v>54002600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48172600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>49657800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>50550200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37940300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>44721000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>39647000</v>
+        <v>38707000</v>
       </c>
       <c r="E62" s="3">
-        <v>38001000</v>
+        <v>39760300</v>
       </c>
       <c r="F62" s="3">
-        <v>36985500</v>
+        <v>38109600</v>
       </c>
       <c r="G62" s="3">
-        <v>23303600</v>
+        <v>37091200</v>
       </c>
       <c r="H62" s="3">
-        <v>23676900</v>
+        <v>23370200</v>
       </c>
       <c r="I62" s="3">
-        <v>25148100</v>
+        <v>23744500</v>
       </c>
       <c r="J62" s="3">
+        <v>25220000</v>
+      </c>
+      <c r="K62" s="3">
         <v>29015100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>25551600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26100300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25514900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28140600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30198600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>271285000</v>
+        <v>253941000</v>
       </c>
       <c r="E66" s="3">
-        <v>259259000</v>
+        <v>272060000</v>
       </c>
       <c r="F66" s="3">
-        <v>248460000</v>
+        <v>259999000</v>
       </c>
       <c r="G66" s="3">
-        <v>150777000</v>
+        <v>249170000</v>
       </c>
       <c r="H66" s="3">
-        <v>124198000</v>
+        <v>151208000</v>
       </c>
       <c r="I66" s="3">
-        <v>120002000</v>
+        <v>124553000</v>
       </c>
       <c r="J66" s="3">
+        <v>120345000</v>
+      </c>
+      <c r="K66" s="3">
         <v>129310000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>116902000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>117340000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112765000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>90051400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>102232000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-28739500</v>
+        <v>-13145300</v>
       </c>
       <c r="E72" s="3">
-        <v>-34917500</v>
+        <v>-28821600</v>
       </c>
       <c r="F72" s="3">
-        <v>-37700500</v>
+        <v>-35017200</v>
       </c>
       <c r="G72" s="3">
-        <v>-37803600</v>
+        <v>-37808200</v>
       </c>
       <c r="H72" s="3">
-        <v>-38220200</v>
+        <v>-37911600</v>
       </c>
       <c r="I72" s="3">
-        <v>-38288600</v>
+        <v>-38329400</v>
       </c>
       <c r="J72" s="3">
+        <v>-38398000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-39116400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-36457900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-41617500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-43669700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-75680700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-58425200</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>52685400</v>
+        <v>61940100</v>
       </c>
       <c r="E76" s="3">
-        <v>46306700</v>
+        <v>52836000</v>
       </c>
       <c r="F76" s="3">
-        <v>38975400</v>
+        <v>46439000</v>
       </c>
       <c r="G76" s="3">
-        <v>34402100</v>
+        <v>39086700</v>
       </c>
       <c r="H76" s="3">
-        <v>33534100</v>
+        <v>34500400</v>
       </c>
       <c r="I76" s="3">
-        <v>33345300</v>
+        <v>33629900</v>
       </c>
       <c r="J76" s="3">
+        <v>33440600</v>
+      </c>
+      <c r="K76" s="3">
         <v>31795900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30011500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28720900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28564100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28468900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41555200</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8681100</v>
+        <v>19355100</v>
       </c>
       <c r="E81" s="3">
-        <v>4531000</v>
+        <v>8705900</v>
       </c>
       <c r="F81" s="3">
-        <v>4511400</v>
+        <v>4543900</v>
       </c>
       <c r="G81" s="3">
-        <v>4195700</v>
+        <v>4524300</v>
       </c>
       <c r="H81" s="3">
-        <v>2350100</v>
+        <v>4207700</v>
       </c>
       <c r="I81" s="3">
-        <v>3755200</v>
+        <v>2356800</v>
       </c>
       <c r="J81" s="3">
+        <v>3765900</v>
+      </c>
+      <c r="K81" s="3">
         <v>2902400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3321700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3301500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1112500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5877600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>653800</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>28917400</v>
+        <v>26087200</v>
       </c>
       <c r="E83" s="3">
-        <v>29505500</v>
+        <v>30278600</v>
       </c>
       <c r="F83" s="3">
-        <v>26993700</v>
+        <v>29589800</v>
       </c>
       <c r="G83" s="3">
-        <v>18818200</v>
+        <v>27070800</v>
       </c>
       <c r="H83" s="3">
-        <v>15012100</v>
+        <v>18872000</v>
       </c>
       <c r="I83" s="3">
-        <v>15825800</v>
+        <v>15055000</v>
       </c>
       <c r="J83" s="3">
+        <v>15871000</v>
+      </c>
+      <c r="K83" s="3">
         <v>14517300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>11596300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11939100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13043400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24108800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>16945100</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>38844100</v>
+        <v>40610100</v>
       </c>
       <c r="E89" s="3">
-        <v>34979300</v>
+        <v>38955100</v>
       </c>
       <c r="F89" s="3">
-        <v>25683000</v>
+        <v>35079300</v>
       </c>
       <c r="G89" s="3">
-        <v>25035300</v>
+        <v>25756400</v>
       </c>
       <c r="H89" s="3">
-        <v>19464900</v>
+        <v>25106800</v>
       </c>
       <c r="I89" s="3">
-        <v>18660900</v>
+        <v>19520500</v>
       </c>
       <c r="J89" s="3">
+        <v>18714200</v>
+      </c>
+      <c r="K89" s="3">
         <v>16850100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15310000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15158200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15532700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14907500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19032200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-17970900</v>
+        <v>-13390200</v>
       </c>
       <c r="E91" s="3">
-        <v>-14773400</v>
+        <v>-18022200</v>
       </c>
       <c r="F91" s="3">
-        <v>-14037700</v>
+        <v>-14815600</v>
       </c>
       <c r="G91" s="3">
-        <v>-10830500</v>
+        <v>-14077800</v>
       </c>
       <c r="H91" s="3">
-        <v>-9915800</v>
+        <v>-10861400</v>
       </c>
       <c r="I91" s="3">
-        <v>-9926700</v>
+        <v>-9944100</v>
       </c>
       <c r="J91" s="3">
+        <v>-9955000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8720100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8336900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8113700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7859000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6171900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9867000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-24202000</v>
+        <v>-11112800</v>
       </c>
       <c r="E94" s="3">
-        <v>-29732300</v>
+        <v>-24271200</v>
       </c>
       <c r="F94" s="3">
-        <v>-24574200</v>
+        <v>-29817200</v>
       </c>
       <c r="G94" s="3">
-        <v>-15439600</v>
+        <v>-24644400</v>
       </c>
       <c r="H94" s="3">
-        <v>-15512200</v>
+        <v>-15483700</v>
       </c>
       <c r="I94" s="3">
-        <v>-18243200</v>
+        <v>-15556600</v>
       </c>
       <c r="J94" s="3">
+        <v>-18295300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-14764700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-15327300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12150200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11837600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7324800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10887100</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3672700</v>
+        <v>-4381800</v>
       </c>
       <c r="E96" s="3">
-        <v>-3412300</v>
+        <v>-3683200</v>
       </c>
       <c r="F96" s="3">
-        <v>-3327700</v>
+        <v>-3422100</v>
       </c>
       <c r="G96" s="3">
-        <v>-3863700</v>
+        <v>-3337200</v>
       </c>
       <c r="H96" s="3">
-        <v>-3344000</v>
+        <v>-3874700</v>
       </c>
       <c r="I96" s="3">
-        <v>-1691500</v>
+        <v>-3353500</v>
       </c>
       <c r="J96" s="3">
+        <v>-1696300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1731700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1282100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1456500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2683100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3733200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-4133000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-16750200</v>
+        <v>-27783500</v>
       </c>
       <c r="E100" s="3">
-        <v>-11695200</v>
+        <v>-16798100</v>
       </c>
       <c r="F100" s="3">
-        <v>8203700</v>
+        <v>-11728600</v>
       </c>
       <c r="G100" s="3">
-        <v>-7748000</v>
+        <v>8227100</v>
       </c>
       <c r="H100" s="3">
-        <v>-3536000</v>
+        <v>-7770100</v>
       </c>
       <c r="I100" s="3">
-        <v>-4984500</v>
+        <v>-3546100</v>
       </c>
       <c r="J100" s="3">
+        <v>-4998700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1434400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-894200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3877300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1222500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7247900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6993600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100900</v>
+        <v>-74000</v>
       </c>
       <c r="E101" s="3">
-        <v>672700</v>
+        <v>101200</v>
       </c>
       <c r="F101" s="3">
-        <v>-1124100</v>
+        <v>674600</v>
       </c>
       <c r="G101" s="3">
-        <v>11900</v>
+        <v>-1127300</v>
       </c>
       <c r="H101" s="3">
-        <v>-18400</v>
+        <v>12000</v>
       </c>
       <c r="I101" s="3">
-        <v>-245200</v>
+        <v>-18500</v>
       </c>
       <c r="J101" s="3">
+        <v>-245900</v>
+      </c>
+      <c r="K101" s="3">
         <v>271300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>272600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>364700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-199800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-30700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-47000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-2007300</v>
+        <v>1639800</v>
       </c>
       <c r="E102" s="3">
-        <v>-5775500</v>
+        <v>-2013000</v>
       </c>
       <c r="F102" s="3">
-        <v>8188500</v>
+        <v>-5792000</v>
       </c>
       <c r="G102" s="3">
-        <v>1859700</v>
+        <v>8211900</v>
       </c>
       <c r="H102" s="3">
-        <v>398200</v>
+        <v>1865000</v>
       </c>
       <c r="I102" s="3">
-        <v>-4812000</v>
+        <v>399300</v>
       </c>
       <c r="J102" s="3">
+        <v>-4825700</v>
+      </c>
+      <c r="K102" s="3">
         <v>922300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-639000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-504700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>4717800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>304100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1104600</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>121834600</v>
+        <v>121006000</v>
       </c>
       <c r="E8" s="3">
-        <v>124257800</v>
+        <v>123412700</v>
       </c>
       <c r="F8" s="3">
-        <v>117090400</v>
+        <v>116294100</v>
       </c>
       <c r="G8" s="3">
-        <v>109897000</v>
+        <v>109149600</v>
       </c>
       <c r="H8" s="3">
-        <v>87625800</v>
+        <v>87029900</v>
       </c>
       <c r="I8" s="3">
-        <v>82321300</v>
+        <v>81761400</v>
       </c>
       <c r="J8" s="3">
-        <v>81549800</v>
+        <v>80995200</v>
       </c>
       <c r="K8" s="3">
         <v>79308100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>48405200</v>
+        <v>48076000</v>
       </c>
       <c r="E9" s="3">
-        <v>54457200</v>
+        <v>54086900</v>
       </c>
       <c r="F9" s="3">
-        <v>50689100</v>
+        <v>50344400</v>
       </c>
       <c r="G9" s="3">
-        <v>45607700</v>
+        <v>45297500</v>
       </c>
       <c r="H9" s="3">
-        <v>37549200</v>
+        <v>37293900</v>
       </c>
       <c r="I9" s="3">
-        <v>38889800</v>
+        <v>38625300</v>
       </c>
       <c r="J9" s="3">
-        <v>39006200</v>
+        <v>38740900</v>
       </c>
       <c r="K9" s="3">
         <v>37957600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>73429300</v>
+        <v>72930000</v>
       </c>
       <c r="E10" s="3">
-        <v>69800500</v>
+        <v>69325800</v>
       </c>
       <c r="F10" s="3">
-        <v>66401300</v>
+        <v>65949700</v>
       </c>
       <c r="G10" s="3">
-        <v>64289300</v>
+        <v>63852100</v>
       </c>
       <c r="H10" s="3">
-        <v>50076500</v>
+        <v>49736000</v>
       </c>
       <c r="I10" s="3">
-        <v>43431500</v>
+        <v>43136100</v>
       </c>
       <c r="J10" s="3">
-        <v>42543600</v>
+        <v>42254300</v>
       </c>
       <c r="K10" s="3">
         <v>41350400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1230600</v>
+        <v>1222300</v>
       </c>
       <c r="E14" s="3">
-        <v>-556000</v>
+        <v>-552200</v>
       </c>
       <c r="F14" s="3">
-        <v>915100</v>
+        <v>908900</v>
       </c>
       <c r="G14" s="3">
-        <v>192600</v>
+        <v>191300</v>
       </c>
       <c r="H14" s="3">
-        <v>799800</v>
+        <v>794300</v>
       </c>
       <c r="I14" s="3">
-        <v>1310100</v>
+        <v>1301200</v>
       </c>
       <c r="J14" s="3">
-        <v>534300</v>
+        <v>530600</v>
       </c>
       <c r="K14" s="3">
         <v>732400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>25846700</v>
+        <v>25670900</v>
       </c>
       <c r="E15" s="3">
-        <v>29020700</v>
+        <v>28823300</v>
       </c>
       <c r="F15" s="3">
-        <v>29594100</v>
+        <v>29392900</v>
       </c>
       <c r="G15" s="3">
-        <v>27236200</v>
+        <v>27051000</v>
       </c>
       <c r="H15" s="3">
-        <v>18791500</v>
+        <v>18663700</v>
       </c>
       <c r="I15" s="3">
-        <v>14269300</v>
+        <v>14172300</v>
       </c>
       <c r="J15" s="3">
-        <v>13525100</v>
+        <v>13433100</v>
       </c>
       <c r="K15" s="3">
         <v>13766500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>99204300</v>
+        <v>98529600</v>
       </c>
       <c r="E17" s="3">
-        <v>107485800</v>
+        <v>106754800</v>
       </c>
       <c r="F17" s="3">
-        <v>103416300</v>
+        <v>102713000</v>
       </c>
       <c r="G17" s="3">
-        <v>95965000</v>
+        <v>95312300</v>
       </c>
       <c r="H17" s="3">
-        <v>77335600</v>
+        <v>76809700</v>
       </c>
       <c r="I17" s="3">
-        <v>73588200</v>
+        <v>73087700</v>
       </c>
       <c r="J17" s="3">
-        <v>71340200</v>
+        <v>70855000</v>
       </c>
       <c r="K17" s="3">
         <v>69365100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>22630300</v>
+        <v>22476400</v>
       </c>
       <c r="E18" s="3">
-        <v>16772000</v>
+        <v>16657900</v>
       </c>
       <c r="F18" s="3">
-        <v>13674200</v>
+        <v>13581200</v>
       </c>
       <c r="G18" s="3">
-        <v>13932000</v>
+        <v>13837300</v>
       </c>
       <c r="H18" s="3">
-        <v>10290200</v>
+        <v>10220200</v>
       </c>
       <c r="I18" s="3">
-        <v>8733100</v>
+        <v>8673700</v>
       </c>
       <c r="J18" s="3">
-        <v>10209600</v>
+        <v>10140200</v>
       </c>
       <c r="K18" s="3">
         <v>9942900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2439500</v>
+        <v>-2422900</v>
       </c>
       <c r="E20" s="3">
-        <v>1351400</v>
+        <v>1342200</v>
       </c>
       <c r="F20" s="3">
-        <v>95800</v>
+        <v>95100</v>
       </c>
       <c r="G20" s="3">
-        <v>556000</v>
+        <v>552200</v>
       </c>
       <c r="H20" s="3">
-        <v>560400</v>
+        <v>556600</v>
       </c>
       <c r="I20" s="3">
-        <v>-847600</v>
+        <v>-841900</v>
       </c>
       <c r="J20" s="3">
-        <v>-2036900</v>
+        <v>-2023100</v>
       </c>
       <c r="K20" s="3">
         <v>-2063700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>46433600</v>
+        <v>45800000</v>
       </c>
       <c r="E21" s="3">
-        <v>48582500</v>
+        <v>47883300</v>
       </c>
       <c r="F21" s="3">
-        <v>43536200</v>
+        <v>42879600</v>
       </c>
       <c r="G21" s="3">
-        <v>41720400</v>
+        <v>41106800</v>
       </c>
       <c r="H21" s="3">
-        <v>29835100</v>
+        <v>29402300</v>
       </c>
       <c r="I21" s="3">
-        <v>23030200</v>
+        <v>22690200</v>
       </c>
       <c r="J21" s="3">
-        <v>24138400</v>
+        <v>23780900</v>
       </c>
       <c r="K21" s="3">
         <v>22391200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7168400</v>
+        <v>7119700</v>
       </c>
       <c r="E22" s="3">
-        <v>6179300</v>
+        <v>6137300</v>
       </c>
       <c r="F22" s="3">
-        <v>5469900</v>
+        <v>5432700</v>
       </c>
       <c r="G22" s="3">
-        <v>5046600</v>
+        <v>5012300</v>
       </c>
       <c r="H22" s="3">
-        <v>2950900</v>
+        <v>2930900</v>
       </c>
       <c r="I22" s="3">
-        <v>2278500</v>
+        <v>2263000</v>
       </c>
       <c r="J22" s="3">
-        <v>2738700</v>
+        <v>2720100</v>
       </c>
       <c r="K22" s="3">
         <v>2945800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>13022400</v>
+        <v>12933800</v>
       </c>
       <c r="E23" s="3">
-        <v>11944100</v>
+        <v>11862800</v>
       </c>
       <c r="F23" s="3">
-        <v>8300000</v>
+        <v>8243600</v>
       </c>
       <c r="G23" s="3">
-        <v>9441400</v>
+        <v>9377200</v>
       </c>
       <c r="H23" s="3">
-        <v>7899600</v>
+        <v>7845900</v>
       </c>
       <c r="I23" s="3">
-        <v>5607000</v>
+        <v>5568800</v>
       </c>
       <c r="J23" s="3">
-        <v>5434000</v>
+        <v>5397000</v>
       </c>
       <c r="K23" s="3">
         <v>4933500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3995500</v>
+        <v>3968300</v>
       </c>
       <c r="E24" s="3">
-        <v>2107600</v>
+        <v>2093300</v>
       </c>
       <c r="F24" s="3">
-        <v>1884600</v>
+        <v>1871800</v>
       </c>
       <c r="G24" s="3">
-        <v>2098900</v>
+        <v>2084700</v>
       </c>
       <c r="H24" s="3">
-        <v>2168600</v>
+        <v>2153800</v>
       </c>
       <c r="I24" s="3">
-        <v>1984700</v>
+        <v>1971200</v>
       </c>
       <c r="J24" s="3">
-        <v>-607200</v>
+        <v>-603000</v>
       </c>
       <c r="K24" s="3">
         <v>1565700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9026900</v>
+        <v>8965500</v>
       </c>
       <c r="E26" s="3">
-        <v>9836400</v>
+        <v>9769500</v>
       </c>
       <c r="F26" s="3">
-        <v>6415400</v>
+        <v>6371800</v>
       </c>
       <c r="G26" s="3">
-        <v>7342500</v>
+        <v>7292600</v>
       </c>
       <c r="H26" s="3">
-        <v>5731000</v>
+        <v>5692000</v>
       </c>
       <c r="I26" s="3">
-        <v>3622300</v>
+        <v>3597700</v>
       </c>
       <c r="J26" s="3">
-        <v>6041100</v>
+        <v>6000000</v>
       </c>
       <c r="K26" s="3">
         <v>3367800</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4452500</v>
+        <v>4422200</v>
       </c>
       <c r="E27" s="3">
-        <v>8223900</v>
+        <v>8167900</v>
       </c>
       <c r="F27" s="3">
-        <v>4318700</v>
+        <v>4289300</v>
       </c>
       <c r="G27" s="3">
-        <v>4524300</v>
+        <v>4493600</v>
       </c>
       <c r="H27" s="3">
-        <v>4207700</v>
+        <v>4179100</v>
       </c>
       <c r="I27" s="3">
-        <v>2356800</v>
+        <v>2340800</v>
       </c>
       <c r="J27" s="3">
-        <v>3765900</v>
+        <v>3740300</v>
       </c>
       <c r="K27" s="3">
         <v>2902400</v>
@@ -1590,13 +1590,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>14902600</v>
+        <v>14801300</v>
       </c>
       <c r="E29" s="3">
-        <v>482000</v>
+        <v>478800</v>
       </c>
       <c r="F29" s="3">
-        <v>225200</v>
+        <v>223700</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2439500</v>
+        <v>2422900</v>
       </c>
       <c r="E32" s="3">
-        <v>-1351400</v>
+        <v>-1342200</v>
       </c>
       <c r="F32" s="3">
-        <v>-95800</v>
+        <v>-95100</v>
       </c>
       <c r="G32" s="3">
-        <v>-556000</v>
+        <v>-552200</v>
       </c>
       <c r="H32" s="3">
-        <v>-560400</v>
+        <v>-556600</v>
       </c>
       <c r="I32" s="3">
-        <v>847600</v>
+        <v>841900</v>
       </c>
       <c r="J32" s="3">
-        <v>2036900</v>
+        <v>2023100</v>
       </c>
       <c r="K32" s="3">
         <v>2063700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>19355100</v>
+        <v>19223500</v>
       </c>
       <c r="E33" s="3">
-        <v>8705900</v>
+        <v>8646700</v>
       </c>
       <c r="F33" s="3">
-        <v>4543900</v>
+        <v>4513000</v>
       </c>
       <c r="G33" s="3">
-        <v>4524300</v>
+        <v>4493600</v>
       </c>
       <c r="H33" s="3">
-        <v>4207700</v>
+        <v>4179100</v>
       </c>
       <c r="I33" s="3">
-        <v>2356800</v>
+        <v>2340800</v>
       </c>
       <c r="J33" s="3">
-        <v>3765900</v>
+        <v>3740300</v>
       </c>
       <c r="K33" s="3">
         <v>2902400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>19355100</v>
+        <v>19223500</v>
       </c>
       <c r="E35" s="3">
-        <v>8705900</v>
+        <v>8646700</v>
       </c>
       <c r="F35" s="3">
-        <v>4543900</v>
+        <v>4513000</v>
       </c>
       <c r="G35" s="3">
-        <v>4524300</v>
+        <v>4493600</v>
       </c>
       <c r="H35" s="3">
-        <v>4207700</v>
+        <v>4179100</v>
       </c>
       <c r="I35" s="3">
-        <v>2356800</v>
+        <v>2340800</v>
       </c>
       <c r="J35" s="3">
-        <v>3765900</v>
+        <v>3740300</v>
       </c>
       <c r="K35" s="3">
         <v>2902400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7914800</v>
+        <v>7861000</v>
       </c>
       <c r="E41" s="3">
-        <v>6275100</v>
+        <v>6232400</v>
       </c>
       <c r="F41" s="3">
-        <v>8288100</v>
+        <v>8231700</v>
       </c>
       <c r="G41" s="3">
-        <v>14078900</v>
+        <v>13983200</v>
       </c>
       <c r="H41" s="3">
-        <v>5868100</v>
+        <v>5828200</v>
       </c>
       <c r="I41" s="3">
-        <v>4003100</v>
+        <v>3975900</v>
       </c>
       <c r="J41" s="3">
-        <v>3603800</v>
+        <v>3579300</v>
       </c>
       <c r="K41" s="3">
         <v>8405500</v>
@@ -2038,22 +2038,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>119700</v>
+        <v>118900</v>
       </c>
       <c r="E42" s="3">
-        <v>103400</v>
+        <v>102700</v>
       </c>
       <c r="F42" s="3">
-        <v>101200</v>
+        <v>100500</v>
       </c>
       <c r="G42" s="3">
-        <v>101200</v>
+        <v>100500</v>
       </c>
       <c r="H42" s="3">
-        <v>31600</v>
+        <v>31300</v>
       </c>
       <c r="I42" s="3">
-        <v>13100</v>
+        <v>13000</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25611700</v>
+        <v>25437500</v>
       </c>
       <c r="E43" s="3">
-        <v>26120900</v>
+        <v>25943300</v>
       </c>
       <c r="F43" s="3">
-        <v>23310400</v>
+        <v>23151800</v>
       </c>
       <c r="G43" s="3">
-        <v>20591200</v>
+        <v>20451200</v>
       </c>
       <c r="H43" s="3">
-        <v>17779600</v>
+        <v>17658600</v>
       </c>
       <c r="I43" s="3">
-        <v>16244200</v>
+        <v>16133800</v>
       </c>
       <c r="J43" s="3">
-        <v>14117000</v>
+        <v>14021000</v>
       </c>
       <c r="K43" s="3">
         <v>15932100</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2632100</v>
+        <v>2614200</v>
       </c>
       <c r="E44" s="3">
-        <v>2871500</v>
+        <v>2852000</v>
       </c>
       <c r="F44" s="3">
-        <v>3106500</v>
+        <v>3085400</v>
       </c>
       <c r="G44" s="3">
-        <v>2932400</v>
+        <v>2912500</v>
       </c>
       <c r="H44" s="3">
-        <v>1706100</v>
+        <v>1694500</v>
       </c>
       <c r="I44" s="3">
-        <v>1947700</v>
+        <v>1934500</v>
       </c>
       <c r="J44" s="3">
-        <v>2159900</v>
+        <v>2145200</v>
       </c>
       <c r="K44" s="3">
         <v>1767500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3288200</v>
+        <v>3265900</v>
       </c>
       <c r="E45" s="3">
-        <v>7221700</v>
+        <v>7172600</v>
       </c>
       <c r="F45" s="3">
-        <v>7411000</v>
+        <v>7360600</v>
       </c>
       <c r="G45" s="3">
-        <v>2874800</v>
+        <v>2855200</v>
       </c>
       <c r="H45" s="3">
-        <v>1478700</v>
+        <v>1468700</v>
       </c>
       <c r="I45" s="3">
-        <v>1588600</v>
+        <v>1577800</v>
       </c>
       <c r="J45" s="3">
-        <v>2307900</v>
+        <v>2292200</v>
       </c>
       <c r="K45" s="3">
         <v>2795000</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>39566600</v>
+        <v>39297500</v>
       </c>
       <c r="E46" s="3">
-        <v>42592600</v>
+        <v>42302900</v>
       </c>
       <c r="F46" s="3">
-        <v>42217200</v>
+        <v>41930100</v>
       </c>
       <c r="G46" s="3">
-        <v>40578500</v>
+        <v>40302500</v>
       </c>
       <c r="H46" s="3">
-        <v>26864100</v>
+        <v>26681400</v>
       </c>
       <c r="I46" s="3">
-        <v>23796700</v>
+        <v>23634900</v>
       </c>
       <c r="J46" s="3">
-        <v>22188500</v>
+        <v>22037600</v>
       </c>
       <c r="K46" s="3">
         <v>28902200</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9515400</v>
+        <v>9450700</v>
       </c>
       <c r="E47" s="3">
-        <v>6922500</v>
+        <v>6875400</v>
       </c>
       <c r="F47" s="3">
-        <v>6282700</v>
+        <v>6240000</v>
       </c>
       <c r="G47" s="3">
-        <v>7572100</v>
+        <v>7520600</v>
       </c>
       <c r="H47" s="3">
-        <v>4880100</v>
+        <v>4846900</v>
       </c>
       <c r="I47" s="3">
-        <v>2351400</v>
+        <v>2335400</v>
       </c>
       <c r="J47" s="3">
-        <v>6927900</v>
+        <v>6880800</v>
       </c>
       <c r="K47" s="3">
         <v>9342900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>106490000</v>
+        <v>105766000</v>
       </c>
       <c r="E48" s="3">
-        <v>108218000</v>
+        <v>107482000</v>
       </c>
       <c r="F48" s="3">
-        <v>100700000</v>
+        <v>100016000</v>
       </c>
       <c r="G48" s="3">
-        <v>99318500</v>
+        <v>98643100</v>
       </c>
       <c r="H48" s="3">
-        <v>73496800</v>
+        <v>72997000</v>
       </c>
       <c r="I48" s="3">
-        <v>55091600</v>
+        <v>54716900</v>
       </c>
       <c r="J48" s="3">
-        <v>51008000</v>
+        <v>50661100</v>
       </c>
       <c r="K48" s="3">
         <v>50732400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>147986000</v>
+        <v>146980000</v>
       </c>
       <c r="E49" s="3">
-        <v>152987000</v>
+        <v>151946000</v>
       </c>
       <c r="F49" s="3">
-        <v>144333000</v>
+        <v>143352000</v>
       </c>
       <c r="G49" s="3">
-        <v>128468000</v>
+        <v>127594000</v>
       </c>
       <c r="H49" s="3">
-        <v>74210600</v>
+        <v>73705900</v>
       </c>
       <c r="I49" s="3">
-        <v>70672100</v>
+        <v>70191500</v>
       </c>
       <c r="J49" s="3">
-        <v>68403400</v>
+        <v>67938200</v>
       </c>
       <c r="K49" s="3">
         <v>65749900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12322700</v>
+        <v>12238900</v>
       </c>
       <c r="E52" s="3">
-        <v>14175800</v>
+        <v>14079400</v>
       </c>
       <c r="F52" s="3">
-        <v>12904900</v>
+        <v>12817100</v>
       </c>
       <c r="G52" s="3">
-        <v>12319500</v>
+        <v>12235700</v>
       </c>
       <c r="H52" s="3">
-        <v>6256600</v>
+        <v>6214000</v>
       </c>
       <c r="I52" s="3">
-        <v>6270700</v>
+        <v>6228100</v>
       </c>
       <c r="J52" s="3">
-        <v>5257700</v>
+        <v>5221900</v>
       </c>
       <c r="K52" s="3">
         <v>6378700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>315881000</v>
+        <v>313733000</v>
       </c>
       <c r="E54" s="3">
-        <v>324896000</v>
+        <v>322686000</v>
       </c>
       <c r="F54" s="3">
-        <v>306438000</v>
+        <v>304354000</v>
       </c>
       <c r="G54" s="3">
-        <v>288256000</v>
+        <v>286296000</v>
       </c>
       <c r="H54" s="3">
-        <v>185708000</v>
+        <v>184445000</v>
       </c>
       <c r="I54" s="3">
-        <v>158183000</v>
+        <v>157107000</v>
       </c>
       <c r="J54" s="3">
-        <v>153786000</v>
+        <v>152740000</v>
       </c>
       <c r="K54" s="3">
         <v>161106000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11727500</v>
+        <v>11647800</v>
       </c>
       <c r="E57" s="3">
-        <v>13036500</v>
+        <v>12947900</v>
       </c>
       <c r="F57" s="3">
-        <v>11311900</v>
+        <v>11235000</v>
       </c>
       <c r="G57" s="3">
-        <v>10544800</v>
+        <v>10473100</v>
       </c>
       <c r="H57" s="3">
-        <v>10239000</v>
+        <v>10169400</v>
       </c>
       <c r="I57" s="3">
-        <v>11641600</v>
+        <v>11562400</v>
       </c>
       <c r="J57" s="3">
-        <v>11897300</v>
+        <v>11816400</v>
       </c>
       <c r="K57" s="3">
         <v>11271000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14571800</v>
+        <v>14472700</v>
       </c>
       <c r="E58" s="3">
-        <v>19395400</v>
+        <v>19263500</v>
       </c>
       <c r="F58" s="3">
-        <v>17123400</v>
+        <v>17007000</v>
       </c>
       <c r="G58" s="3">
-        <v>17531500</v>
+        <v>17412200</v>
       </c>
       <c r="H58" s="3">
-        <v>14159400</v>
+        <v>14063100</v>
       </c>
       <c r="I58" s="3">
-        <v>9376200</v>
+        <v>9312400</v>
       </c>
       <c r="J58" s="3">
-        <v>7564500</v>
+        <v>7513000</v>
       </c>
       <c r="K58" s="3">
         <v>12321300</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12942900</v>
+        <v>12854900</v>
       </c>
       <c r="E59" s="3">
-        <v>16955900</v>
+        <v>16840500</v>
       </c>
       <c r="F59" s="3">
-        <v>13786200</v>
+        <v>13692500</v>
       </c>
       <c r="G59" s="3">
-        <v>12330300</v>
+        <v>12246500</v>
       </c>
       <c r="H59" s="3">
-        <v>11414200</v>
+        <v>11336500</v>
       </c>
       <c r="I59" s="3">
-        <v>10693800</v>
+        <v>10621100</v>
       </c>
       <c r="J59" s="3">
-        <v>10315200</v>
+        <v>10245000</v>
       </c>
       <c r="K59" s="3">
         <v>12349500</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>39242300</v>
+        <v>38975400</v>
       </c>
       <c r="E60" s="3">
-        <v>49387800</v>
+        <v>49051900</v>
       </c>
       <c r="F60" s="3">
-        <v>42221500</v>
+        <v>41934400</v>
       </c>
       <c r="G60" s="3">
-        <v>40406600</v>
+        <v>40131800</v>
       </c>
       <c r="H60" s="3">
-        <v>35812600</v>
+        <v>35569100</v>
       </c>
       <c r="I60" s="3">
-        <v>31711600</v>
+        <v>31495900</v>
       </c>
       <c r="J60" s="3">
-        <v>29776900</v>
+        <v>29574400</v>
       </c>
       <c r="K60" s="3">
         <v>35941700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>138657000</v>
+        <v>137714000</v>
       </c>
       <c r="E61" s="3">
-        <v>140735000</v>
+        <v>139778000</v>
       </c>
       <c r="F61" s="3">
-        <v>137461000</v>
+        <v>136526000</v>
       </c>
       <c r="G61" s="3">
-        <v>131817000</v>
+        <v>130920000</v>
       </c>
       <c r="H61" s="3">
-        <v>76221400</v>
+        <v>75703000</v>
       </c>
       <c r="I61" s="3">
-        <v>55462600</v>
+        <v>55085400</v>
       </c>
       <c r="J61" s="3">
-        <v>52577000</v>
+        <v>52219400</v>
       </c>
       <c r="K61" s="3">
         <v>54002600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>38707000</v>
+        <v>38443700</v>
       </c>
       <c r="E62" s="3">
-        <v>39760300</v>
+        <v>39489900</v>
       </c>
       <c r="F62" s="3">
-        <v>38109600</v>
+        <v>37850400</v>
       </c>
       <c r="G62" s="3">
-        <v>37091200</v>
+        <v>36838900</v>
       </c>
       <c r="H62" s="3">
-        <v>23370200</v>
+        <v>23211300</v>
       </c>
       <c r="I62" s="3">
-        <v>23744500</v>
+        <v>23583000</v>
       </c>
       <c r="J62" s="3">
-        <v>25220000</v>
+        <v>25048500</v>
       </c>
       <c r="K62" s="3">
         <v>29015100</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>253941000</v>
+        <v>252214000</v>
       </c>
       <c r="E66" s="3">
-        <v>272060000</v>
+        <v>270210000</v>
       </c>
       <c r="F66" s="3">
-        <v>259999000</v>
+        <v>258231000</v>
       </c>
       <c r="G66" s="3">
-        <v>249170000</v>
+        <v>247475000</v>
       </c>
       <c r="H66" s="3">
-        <v>151208000</v>
+        <v>150180000</v>
       </c>
       <c r="I66" s="3">
-        <v>124553000</v>
+        <v>123706000</v>
       </c>
       <c r="J66" s="3">
-        <v>120345000</v>
+        <v>119527000</v>
       </c>
       <c r="K66" s="3">
         <v>129310000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-13145300</v>
+        <v>-13055900</v>
       </c>
       <c r="E72" s="3">
-        <v>-28821600</v>
+        <v>-28625600</v>
       </c>
       <c r="F72" s="3">
-        <v>-35017200</v>
+        <v>-34779100</v>
       </c>
       <c r="G72" s="3">
-        <v>-37808200</v>
+        <v>-37551100</v>
       </c>
       <c r="H72" s="3">
-        <v>-37911600</v>
+        <v>-37653700</v>
       </c>
       <c r="I72" s="3">
-        <v>-38329400</v>
+        <v>-38068700</v>
       </c>
       <c r="J72" s="3">
-        <v>-38398000</v>
+        <v>-38136800</v>
       </c>
       <c r="K72" s="3">
         <v>-39116400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>61940100</v>
+        <v>61518800</v>
       </c>
       <c r="E76" s="3">
-        <v>52836000</v>
+        <v>52476600</v>
       </c>
       <c r="F76" s="3">
-        <v>46439000</v>
+        <v>46123200</v>
       </c>
       <c r="G76" s="3">
-        <v>39086700</v>
+        <v>38820900</v>
       </c>
       <c r="H76" s="3">
-        <v>34500400</v>
+        <v>34265800</v>
       </c>
       <c r="I76" s="3">
-        <v>33629900</v>
+        <v>33401200</v>
       </c>
       <c r="J76" s="3">
-        <v>33440600</v>
+        <v>33213200</v>
       </c>
       <c r="K76" s="3">
         <v>31795900</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>19355100</v>
+        <v>19223500</v>
       </c>
       <c r="E81" s="3">
-        <v>8705900</v>
+        <v>8646700</v>
       </c>
       <c r="F81" s="3">
-        <v>4543900</v>
+        <v>4513000</v>
       </c>
       <c r="G81" s="3">
-        <v>4524300</v>
+        <v>4493600</v>
       </c>
       <c r="H81" s="3">
-        <v>4207700</v>
+        <v>4179100</v>
       </c>
       <c r="I81" s="3">
-        <v>2356800</v>
+        <v>2340800</v>
       </c>
       <c r="J81" s="3">
-        <v>3765900</v>
+        <v>3740300</v>
       </c>
       <c r="K81" s="3">
         <v>2902400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>26087200</v>
+        <v>25909800</v>
       </c>
       <c r="E83" s="3">
-        <v>30278600</v>
+        <v>30072600</v>
       </c>
       <c r="F83" s="3">
-        <v>29589800</v>
+        <v>29388600</v>
       </c>
       <c r="G83" s="3">
-        <v>27070800</v>
+        <v>26886700</v>
       </c>
       <c r="H83" s="3">
-        <v>18872000</v>
+        <v>18743700</v>
       </c>
       <c r="I83" s="3">
-        <v>15055000</v>
+        <v>14952600</v>
       </c>
       <c r="J83" s="3">
-        <v>15871000</v>
+        <v>15763100</v>
       </c>
       <c r="K83" s="3">
         <v>14517300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>40610100</v>
+        <v>40333900</v>
       </c>
       <c r="E89" s="3">
-        <v>38955100</v>
+        <v>38690100</v>
       </c>
       <c r="F89" s="3">
-        <v>35079300</v>
+        <v>34840700</v>
       </c>
       <c r="G89" s="3">
-        <v>25756400</v>
+        <v>25581200</v>
       </c>
       <c r="H89" s="3">
-        <v>25106800</v>
+        <v>24936100</v>
       </c>
       <c r="I89" s="3">
-        <v>19520500</v>
+        <v>19387800</v>
       </c>
       <c r="J89" s="3">
-        <v>18714200</v>
+        <v>18587000</v>
       </c>
       <c r="K89" s="3">
         <v>16850100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13390200</v>
+        <v>-13299100</v>
       </c>
       <c r="E91" s="3">
-        <v>-18022200</v>
+        <v>-17899600</v>
       </c>
       <c r="F91" s="3">
-        <v>-14815600</v>
+        <v>-14714800</v>
       </c>
       <c r="G91" s="3">
-        <v>-14077800</v>
+        <v>-13982100</v>
       </c>
       <c r="H91" s="3">
-        <v>-10861400</v>
+        <v>-10787500</v>
       </c>
       <c r="I91" s="3">
-        <v>-9944100</v>
+        <v>-9876500</v>
       </c>
       <c r="J91" s="3">
-        <v>-9955000</v>
+        <v>-9887300</v>
       </c>
       <c r="K91" s="3">
         <v>-8720100</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-11112800</v>
+        <v>-11037200</v>
       </c>
       <c r="E94" s="3">
-        <v>-24271200</v>
+        <v>-24106100</v>
       </c>
       <c r="F94" s="3">
-        <v>-29817200</v>
+        <v>-29614400</v>
       </c>
       <c r="G94" s="3">
-        <v>-24644400</v>
+        <v>-24476800</v>
       </c>
       <c r="H94" s="3">
-        <v>-15483700</v>
+        <v>-15378400</v>
       </c>
       <c r="I94" s="3">
-        <v>-15556600</v>
+        <v>-15450800</v>
       </c>
       <c r="J94" s="3">
-        <v>-18295300</v>
+        <v>-18170900</v>
       </c>
       <c r="K94" s="3">
         <v>-14764700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4381800</v>
+        <v>-4352000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3683200</v>
+        <v>-3658200</v>
       </c>
       <c r="F96" s="3">
-        <v>-3422100</v>
+        <v>-3398800</v>
       </c>
       <c r="G96" s="3">
-        <v>-3337200</v>
+        <v>-3314500</v>
       </c>
       <c r="H96" s="3">
-        <v>-3874700</v>
+        <v>-3848400</v>
       </c>
       <c r="I96" s="3">
-        <v>-3353500</v>
+        <v>-3330700</v>
       </c>
       <c r="J96" s="3">
-        <v>-1696300</v>
+        <v>-1684800</v>
       </c>
       <c r="K96" s="3">
         <v>-1731700</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-27783500</v>
+        <v>-27594600</v>
       </c>
       <c r="E100" s="3">
-        <v>-16798100</v>
+        <v>-16683800</v>
       </c>
       <c r="F100" s="3">
-        <v>-11728600</v>
+        <v>-11648900</v>
       </c>
       <c r="G100" s="3">
-        <v>8227100</v>
+        <v>8171200</v>
       </c>
       <c r="H100" s="3">
-        <v>-7770100</v>
+        <v>-7717300</v>
       </c>
       <c r="I100" s="3">
-        <v>-3546100</v>
+        <v>-3522000</v>
       </c>
       <c r="J100" s="3">
-        <v>-4998700</v>
+        <v>-4964700</v>
       </c>
       <c r="K100" s="3">
         <v>-1434400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-74000</v>
+        <v>-73500</v>
       </c>
       <c r="E101" s="3">
-        <v>101200</v>
+        <v>100500</v>
       </c>
       <c r="F101" s="3">
-        <v>674600</v>
+        <v>670000</v>
       </c>
       <c r="G101" s="3">
-        <v>-1127300</v>
+        <v>-1119600</v>
       </c>
       <c r="H101" s="3">
-        <v>12000</v>
+        <v>11900</v>
       </c>
       <c r="I101" s="3">
-        <v>-18500</v>
+        <v>-18400</v>
       </c>
       <c r="J101" s="3">
-        <v>-245900</v>
+        <v>-244200</v>
       </c>
       <c r="K101" s="3">
         <v>271300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1639800</v>
+        <v>1628600</v>
       </c>
       <c r="E102" s="3">
-        <v>-2013000</v>
+        <v>-1999300</v>
       </c>
       <c r="F102" s="3">
-        <v>-5792000</v>
+        <v>-5752600</v>
       </c>
       <c r="G102" s="3">
-        <v>8211900</v>
+        <v>8156000</v>
       </c>
       <c r="H102" s="3">
-        <v>1865000</v>
+        <v>1852300</v>
       </c>
       <c r="I102" s="3">
-        <v>399300</v>
+        <v>396600</v>
       </c>
       <c r="J102" s="3">
-        <v>-4825700</v>
+        <v>-4792900</v>
       </c>
       <c r="K102" s="3">
         <v>922300</v>

--- a/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>121006000</v>
+        <v>124018000</v>
       </c>
       <c r="E8" s="3">
-        <v>123412700</v>
+        <v>126484600</v>
       </c>
       <c r="F8" s="3">
-        <v>116294100</v>
+        <v>119188800</v>
       </c>
       <c r="G8" s="3">
-        <v>109149600</v>
+        <v>111866500</v>
       </c>
       <c r="H8" s="3">
-        <v>87029900</v>
+        <v>89196100</v>
       </c>
       <c r="I8" s="3">
-        <v>81761400</v>
+        <v>83796600</v>
       </c>
       <c r="J8" s="3">
-        <v>80995200</v>
+        <v>83011300</v>
       </c>
       <c r="K8" s="3">
         <v>79308100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>48076000</v>
+        <v>49272700</v>
       </c>
       <c r="E9" s="3">
-        <v>54086900</v>
+        <v>55433200</v>
       </c>
       <c r="F9" s="3">
-        <v>50344400</v>
+        <v>51597500</v>
       </c>
       <c r="G9" s="3">
-        <v>45297500</v>
+        <v>46425100</v>
       </c>
       <c r="H9" s="3">
-        <v>37293900</v>
+        <v>38222200</v>
       </c>
       <c r="I9" s="3">
-        <v>38625300</v>
+        <v>39586700</v>
       </c>
       <c r="J9" s="3">
-        <v>38740900</v>
+        <v>39705200</v>
       </c>
       <c r="K9" s="3">
         <v>37957600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>72930000</v>
+        <v>74745300</v>
       </c>
       <c r="E10" s="3">
-        <v>69325800</v>
+        <v>71051400</v>
       </c>
       <c r="F10" s="3">
-        <v>65949700</v>
+        <v>67591300</v>
       </c>
       <c r="G10" s="3">
-        <v>63852100</v>
+        <v>65441400</v>
       </c>
       <c r="H10" s="3">
-        <v>49736000</v>
+        <v>50974000</v>
       </c>
       <c r="I10" s="3">
-        <v>43136100</v>
+        <v>44209900</v>
       </c>
       <c r="J10" s="3">
-        <v>42254300</v>
+        <v>43306100</v>
       </c>
       <c r="K10" s="3">
         <v>41350400</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1222300</v>
+        <v>1252700</v>
       </c>
       <c r="E14" s="3">
-        <v>-552200</v>
+        <v>-566000</v>
       </c>
       <c r="F14" s="3">
-        <v>908900</v>
+        <v>931500</v>
       </c>
       <c r="G14" s="3">
-        <v>191300</v>
+        <v>196000</v>
       </c>
       <c r="H14" s="3">
-        <v>794300</v>
+        <v>814100</v>
       </c>
       <c r="I14" s="3">
-        <v>1301200</v>
+        <v>1333600</v>
       </c>
       <c r="J14" s="3">
-        <v>530600</v>
+        <v>543800</v>
       </c>
       <c r="K14" s="3">
         <v>732400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>25670900</v>
+        <v>26309900</v>
       </c>
       <c r="E15" s="3">
-        <v>28823300</v>
+        <v>29540800</v>
       </c>
       <c r="F15" s="3">
-        <v>29392900</v>
+        <v>30124500</v>
       </c>
       <c r="G15" s="3">
-        <v>27051000</v>
+        <v>27724300</v>
       </c>
       <c r="H15" s="3">
-        <v>18663700</v>
+        <v>19128300</v>
       </c>
       <c r="I15" s="3">
-        <v>14172300</v>
+        <v>14525100</v>
       </c>
       <c r="J15" s="3">
-        <v>13433100</v>
+        <v>13767500</v>
       </c>
       <c r="K15" s="3">
         <v>13766500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>98529600</v>
+        <v>100982100</v>
       </c>
       <c r="E17" s="3">
-        <v>106754800</v>
+        <v>109412100</v>
       </c>
       <c r="F17" s="3">
-        <v>102713000</v>
+        <v>105269600</v>
       </c>
       <c r="G17" s="3">
-        <v>95312300</v>
+        <v>97684800</v>
       </c>
       <c r="H17" s="3">
-        <v>76809700</v>
+        <v>78721600</v>
       </c>
       <c r="I17" s="3">
-        <v>73087700</v>
+        <v>74907000</v>
       </c>
       <c r="J17" s="3">
-        <v>70855000</v>
+        <v>72618700</v>
       </c>
       <c r="K17" s="3">
         <v>69365100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>22476400</v>
+        <v>23035900</v>
       </c>
       <c r="E18" s="3">
-        <v>16657900</v>
+        <v>17072500</v>
       </c>
       <c r="F18" s="3">
-        <v>13581200</v>
+        <v>13919200</v>
       </c>
       <c r="G18" s="3">
-        <v>13837300</v>
+        <v>14181700</v>
       </c>
       <c r="H18" s="3">
-        <v>10220200</v>
+        <v>10474600</v>
       </c>
       <c r="I18" s="3">
-        <v>8673700</v>
+        <v>8889600</v>
       </c>
       <c r="J18" s="3">
-        <v>10140200</v>
+        <v>10392600</v>
       </c>
       <c r="K18" s="3">
         <v>9942900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2422900</v>
+        <v>-2483200</v>
       </c>
       <c r="E20" s="3">
-        <v>1342200</v>
+        <v>1375600</v>
       </c>
       <c r="F20" s="3">
-        <v>95100</v>
+        <v>97500</v>
       </c>
       <c r="G20" s="3">
-        <v>552200</v>
+        <v>566000</v>
       </c>
       <c r="H20" s="3">
-        <v>556600</v>
+        <v>570400</v>
       </c>
       <c r="I20" s="3">
-        <v>-841900</v>
+        <v>-862800</v>
       </c>
       <c r="J20" s="3">
-        <v>-2023100</v>
+        <v>-2073400</v>
       </c>
       <c r="K20" s="3">
         <v>-2063700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>45800000</v>
+        <v>47102500</v>
       </c>
       <c r="E21" s="3">
-        <v>47883300</v>
+        <v>49263800</v>
       </c>
       <c r="F21" s="3">
-        <v>42879600</v>
+        <v>44131300</v>
       </c>
       <c r="G21" s="3">
-        <v>41106800</v>
+        <v>42298700</v>
       </c>
       <c r="H21" s="3">
-        <v>29402300</v>
+        <v>30251700</v>
       </c>
       <c r="I21" s="3">
-        <v>22690200</v>
+        <v>23348800</v>
       </c>
       <c r="J21" s="3">
-        <v>23780900</v>
+        <v>24471700</v>
       </c>
       <c r="K21" s="3">
         <v>22391200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7119700</v>
+        <v>7296900</v>
       </c>
       <c r="E22" s="3">
-        <v>6137300</v>
+        <v>6290100</v>
       </c>
       <c r="F22" s="3">
-        <v>5432700</v>
+        <v>5567900</v>
       </c>
       <c r="G22" s="3">
-        <v>5012300</v>
+        <v>5137000</v>
       </c>
       <c r="H22" s="3">
-        <v>2930900</v>
+        <v>3003800</v>
       </c>
       <c r="I22" s="3">
-        <v>2263000</v>
+        <v>2319300</v>
       </c>
       <c r="J22" s="3">
-        <v>2720100</v>
+        <v>2787800</v>
       </c>
       <c r="K22" s="3">
         <v>2945800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>12933800</v>
+        <v>13255800</v>
       </c>
       <c r="E23" s="3">
-        <v>11862800</v>
+        <v>12158100</v>
       </c>
       <c r="F23" s="3">
-        <v>8243600</v>
+        <v>8448800</v>
       </c>
       <c r="G23" s="3">
-        <v>9377200</v>
+        <v>9610600</v>
       </c>
       <c r="H23" s="3">
-        <v>7845900</v>
+        <v>8041200</v>
       </c>
       <c r="I23" s="3">
-        <v>5568800</v>
+        <v>5707500</v>
       </c>
       <c r="J23" s="3">
-        <v>5397000</v>
+        <v>5531400</v>
       </c>
       <c r="K23" s="3">
         <v>4933500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3968300</v>
+        <v>4067100</v>
       </c>
       <c r="E24" s="3">
-        <v>2093300</v>
+        <v>2145400</v>
       </c>
       <c r="F24" s="3">
-        <v>1871800</v>
+        <v>1918400</v>
       </c>
       <c r="G24" s="3">
-        <v>2084700</v>
+        <v>2136600</v>
       </c>
       <c r="H24" s="3">
-        <v>2153800</v>
+        <v>2207400</v>
       </c>
       <c r="I24" s="3">
-        <v>1971200</v>
+        <v>2020300</v>
       </c>
       <c r="J24" s="3">
-        <v>-603000</v>
+        <v>-618000</v>
       </c>
       <c r="K24" s="3">
         <v>1565700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8965500</v>
+        <v>9188600</v>
       </c>
       <c r="E26" s="3">
-        <v>9769500</v>
+        <v>10012700</v>
       </c>
       <c r="F26" s="3">
-        <v>6371800</v>
+        <v>6530400</v>
       </c>
       <c r="G26" s="3">
-        <v>7292600</v>
+        <v>7474100</v>
       </c>
       <c r="H26" s="3">
-        <v>5692000</v>
+        <v>5833700</v>
       </c>
       <c r="I26" s="3">
-        <v>3597700</v>
+        <v>3687200</v>
       </c>
       <c r="J26" s="3">
-        <v>6000000</v>
+        <v>6149400</v>
       </c>
       <c r="K26" s="3">
         <v>3367800</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4422200</v>
+        <v>4532300</v>
       </c>
       <c r="E27" s="3">
-        <v>8167900</v>
+        <v>8371200</v>
       </c>
       <c r="F27" s="3">
-        <v>4289300</v>
+        <v>4396100</v>
       </c>
       <c r="G27" s="3">
-        <v>4493600</v>
+        <v>4605400</v>
       </c>
       <c r="H27" s="3">
-        <v>4179100</v>
+        <v>4283100</v>
       </c>
       <c r="I27" s="3">
-        <v>2340800</v>
+        <v>2399100</v>
       </c>
       <c r="J27" s="3">
-        <v>3740300</v>
+        <v>3833400</v>
       </c>
       <c r="K27" s="3">
         <v>2902400</v>
@@ -1590,13 +1590,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>14801300</v>
+        <v>15169700</v>
       </c>
       <c r="E29" s="3">
-        <v>478800</v>
+        <v>490700</v>
       </c>
       <c r="F29" s="3">
-        <v>223700</v>
+        <v>229300</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2422900</v>
+        <v>2483200</v>
       </c>
       <c r="E32" s="3">
-        <v>-1342200</v>
+        <v>-1375600</v>
       </c>
       <c r="F32" s="3">
-        <v>-95100</v>
+        <v>-97500</v>
       </c>
       <c r="G32" s="3">
-        <v>-552200</v>
+        <v>-566000</v>
       </c>
       <c r="H32" s="3">
-        <v>-556600</v>
+        <v>-570400</v>
       </c>
       <c r="I32" s="3">
-        <v>841900</v>
+        <v>862800</v>
       </c>
       <c r="J32" s="3">
-        <v>2023100</v>
+        <v>2073400</v>
       </c>
       <c r="K32" s="3">
         <v>2063700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>19223500</v>
+        <v>19702000</v>
       </c>
       <c r="E33" s="3">
-        <v>8646700</v>
+        <v>8861900</v>
       </c>
       <c r="F33" s="3">
-        <v>4513000</v>
+        <v>4625300</v>
       </c>
       <c r="G33" s="3">
-        <v>4493600</v>
+        <v>4605400</v>
       </c>
       <c r="H33" s="3">
-        <v>4179100</v>
+        <v>4283100</v>
       </c>
       <c r="I33" s="3">
-        <v>2340800</v>
+        <v>2399100</v>
       </c>
       <c r="J33" s="3">
-        <v>3740300</v>
+        <v>3833400</v>
       </c>
       <c r="K33" s="3">
         <v>2902400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>19223500</v>
+        <v>19702000</v>
       </c>
       <c r="E35" s="3">
-        <v>8646700</v>
+        <v>8861900</v>
       </c>
       <c r="F35" s="3">
-        <v>4513000</v>
+        <v>4625300</v>
       </c>
       <c r="G35" s="3">
-        <v>4493600</v>
+        <v>4605400</v>
       </c>
       <c r="H35" s="3">
-        <v>4179100</v>
+        <v>4283100</v>
       </c>
       <c r="I35" s="3">
-        <v>2340800</v>
+        <v>2399100</v>
       </c>
       <c r="J35" s="3">
-        <v>3740300</v>
+        <v>3833400</v>
       </c>
       <c r="K35" s="3">
         <v>2902400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7861000</v>
+        <v>8056700</v>
       </c>
       <c r="E41" s="3">
-        <v>6232400</v>
+        <v>6387500</v>
       </c>
       <c r="F41" s="3">
-        <v>8231700</v>
+        <v>8436600</v>
       </c>
       <c r="G41" s="3">
-        <v>13983200</v>
+        <v>14331200</v>
       </c>
       <c r="H41" s="3">
-        <v>5828200</v>
+        <v>5973300</v>
       </c>
       <c r="I41" s="3">
-        <v>3975900</v>
+        <v>4074900</v>
       </c>
       <c r="J41" s="3">
-        <v>3579300</v>
+        <v>3668400</v>
       </c>
       <c r="K41" s="3">
         <v>8405500</v>
@@ -2038,22 +2038,22 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>118900</v>
+        <v>121800</v>
       </c>
       <c r="E42" s="3">
-        <v>102700</v>
+        <v>105200</v>
       </c>
       <c r="F42" s="3">
-        <v>100500</v>
+        <v>103000</v>
       </c>
       <c r="G42" s="3">
-        <v>100500</v>
+        <v>103000</v>
       </c>
       <c r="H42" s="3">
-        <v>31300</v>
+        <v>32100</v>
       </c>
       <c r="I42" s="3">
-        <v>13000</v>
+        <v>13300</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25437500</v>
+        <v>26070700</v>
       </c>
       <c r="E43" s="3">
-        <v>25943300</v>
+        <v>26589000</v>
       </c>
       <c r="F43" s="3">
-        <v>23151800</v>
+        <v>23728100</v>
       </c>
       <c r="G43" s="3">
-        <v>20451200</v>
+        <v>20960200</v>
       </c>
       <c r="H43" s="3">
-        <v>17658600</v>
+        <v>18098200</v>
       </c>
       <c r="I43" s="3">
-        <v>16133800</v>
+        <v>16535400</v>
       </c>
       <c r="J43" s="3">
-        <v>14021000</v>
+        <v>14370000</v>
       </c>
       <c r="K43" s="3">
         <v>15932100</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2614200</v>
+        <v>2679300</v>
       </c>
       <c r="E44" s="3">
-        <v>2852000</v>
+        <v>2923000</v>
       </c>
       <c r="F44" s="3">
-        <v>3085400</v>
+        <v>3162200</v>
       </c>
       <c r="G44" s="3">
-        <v>2912500</v>
+        <v>2985000</v>
       </c>
       <c r="H44" s="3">
-        <v>1694500</v>
+        <v>1736700</v>
       </c>
       <c r="I44" s="3">
-        <v>1934500</v>
+        <v>1982600</v>
       </c>
       <c r="J44" s="3">
-        <v>2145200</v>
+        <v>2198600</v>
       </c>
       <c r="K44" s="3">
         <v>1767500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3265900</v>
+        <v>3347200</v>
       </c>
       <c r="E45" s="3">
-        <v>7172600</v>
+        <v>7351100</v>
       </c>
       <c r="F45" s="3">
-        <v>7360600</v>
+        <v>7543900</v>
       </c>
       <c r="G45" s="3">
-        <v>2855200</v>
+        <v>2926300</v>
       </c>
       <c r="H45" s="3">
-        <v>1468700</v>
+        <v>1505200</v>
       </c>
       <c r="I45" s="3">
-        <v>1577800</v>
+        <v>1617100</v>
       </c>
       <c r="J45" s="3">
-        <v>2292200</v>
+        <v>2349200</v>
       </c>
       <c r="K45" s="3">
         <v>2795000</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>39297500</v>
+        <v>40275700</v>
       </c>
       <c r="E46" s="3">
-        <v>42302900</v>
+        <v>43355900</v>
       </c>
       <c r="F46" s="3">
-        <v>41930100</v>
+        <v>42973800</v>
       </c>
       <c r="G46" s="3">
-        <v>40302500</v>
+        <v>41305700</v>
       </c>
       <c r="H46" s="3">
-        <v>26681400</v>
+        <v>27345500</v>
       </c>
       <c r="I46" s="3">
-        <v>23634900</v>
+        <v>24223200</v>
       </c>
       <c r="J46" s="3">
-        <v>22037600</v>
+        <v>22586200</v>
       </c>
       <c r="K46" s="3">
         <v>28902200</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9450700</v>
+        <v>9686000</v>
       </c>
       <c r="E47" s="3">
-        <v>6875400</v>
+        <v>7046600</v>
       </c>
       <c r="F47" s="3">
-        <v>6240000</v>
+        <v>6395300</v>
       </c>
       <c r="G47" s="3">
-        <v>7520600</v>
+        <v>7707800</v>
       </c>
       <c r="H47" s="3">
-        <v>4846900</v>
+        <v>4967600</v>
       </c>
       <c r="I47" s="3">
-        <v>2335400</v>
+        <v>2393500</v>
       </c>
       <c r="J47" s="3">
-        <v>6880800</v>
+        <v>7052100</v>
       </c>
       <c r="K47" s="3">
         <v>9342900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>105766000</v>
+        <v>108399000</v>
       </c>
       <c r="E48" s="3">
-        <v>107482000</v>
+        <v>110158000</v>
       </c>
       <c r="F48" s="3">
-        <v>100016000</v>
+        <v>102505000</v>
       </c>
       <c r="G48" s="3">
-        <v>98643100</v>
+        <v>101098000</v>
       </c>
       <c r="H48" s="3">
-        <v>72997000</v>
+        <v>74813900</v>
       </c>
       <c r="I48" s="3">
-        <v>54716900</v>
+        <v>56078900</v>
       </c>
       <c r="J48" s="3">
-        <v>50661100</v>
+        <v>51922100</v>
       </c>
       <c r="K48" s="3">
         <v>50732400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>146980000</v>
+        <v>150638000</v>
       </c>
       <c r="E49" s="3">
-        <v>151946000</v>
+        <v>155729000</v>
       </c>
       <c r="F49" s="3">
-        <v>143352000</v>
+        <v>146920000</v>
       </c>
       <c r="G49" s="3">
-        <v>127594000</v>
+        <v>130770000</v>
       </c>
       <c r="H49" s="3">
-        <v>73705900</v>
+        <v>75540500</v>
       </c>
       <c r="I49" s="3">
-        <v>70191500</v>
+        <v>71938600</v>
       </c>
       <c r="J49" s="3">
-        <v>67938200</v>
+        <v>69629300</v>
       </c>
       <c r="K49" s="3">
         <v>65749900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12238900</v>
+        <v>12543600</v>
       </c>
       <c r="E52" s="3">
-        <v>14079400</v>
+        <v>14429800</v>
       </c>
       <c r="F52" s="3">
-        <v>12817100</v>
+        <v>13136100</v>
       </c>
       <c r="G52" s="3">
-        <v>12235700</v>
+        <v>12540200</v>
       </c>
       <c r="H52" s="3">
-        <v>6214000</v>
+        <v>6368700</v>
       </c>
       <c r="I52" s="3">
-        <v>6228100</v>
+        <v>6383100</v>
       </c>
       <c r="J52" s="3">
-        <v>5221900</v>
+        <v>5351900</v>
       </c>
       <c r="K52" s="3">
         <v>6378700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>313733000</v>
+        <v>321542000</v>
       </c>
       <c r="E54" s="3">
-        <v>322686000</v>
+        <v>330718000</v>
       </c>
       <c r="F54" s="3">
-        <v>304354000</v>
+        <v>311930000</v>
       </c>
       <c r="G54" s="3">
-        <v>286296000</v>
+        <v>293422000</v>
       </c>
       <c r="H54" s="3">
-        <v>184445000</v>
+        <v>189036000</v>
       </c>
       <c r="I54" s="3">
-        <v>157107000</v>
+        <v>161017000</v>
       </c>
       <c r="J54" s="3">
-        <v>152740000</v>
+        <v>156542000</v>
       </c>
       <c r="K54" s="3">
         <v>161106000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11647800</v>
+        <v>11937700</v>
       </c>
       <c r="E57" s="3">
-        <v>12947900</v>
+        <v>13270200</v>
       </c>
       <c r="F57" s="3">
-        <v>11235000</v>
+        <v>11514600</v>
       </c>
       <c r="G57" s="3">
-        <v>10473100</v>
+        <v>10733800</v>
       </c>
       <c r="H57" s="3">
-        <v>10169400</v>
+        <v>10422500</v>
       </c>
       <c r="I57" s="3">
-        <v>11562400</v>
+        <v>11850200</v>
       </c>
       <c r="J57" s="3">
-        <v>11816400</v>
+        <v>12110500</v>
       </c>
       <c r="K57" s="3">
         <v>11271000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14472700</v>
+        <v>14833000</v>
       </c>
       <c r="E58" s="3">
-        <v>19263500</v>
+        <v>19743000</v>
       </c>
       <c r="F58" s="3">
-        <v>17007000</v>
+        <v>17430300</v>
       </c>
       <c r="G58" s="3">
-        <v>17412200</v>
+        <v>17845700</v>
       </c>
       <c r="H58" s="3">
-        <v>14063100</v>
+        <v>14412100</v>
       </c>
       <c r="I58" s="3">
-        <v>9312400</v>
+        <v>9544200</v>
       </c>
       <c r="J58" s="3">
-        <v>7513000</v>
+        <v>7700000</v>
       </c>
       <c r="K58" s="3">
         <v>12321300</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12854900</v>
+        <v>13174900</v>
       </c>
       <c r="E59" s="3">
-        <v>16840500</v>
+        <v>17259700</v>
       </c>
       <c r="F59" s="3">
-        <v>13692500</v>
+        <v>14033300</v>
       </c>
       <c r="G59" s="3">
-        <v>12246500</v>
+        <v>12551300</v>
       </c>
       <c r="H59" s="3">
-        <v>11336500</v>
+        <v>11619800</v>
       </c>
       <c r="I59" s="3">
-        <v>10621100</v>
+        <v>10885500</v>
       </c>
       <c r="J59" s="3">
-        <v>10245000</v>
+        <v>10500000</v>
       </c>
       <c r="K59" s="3">
         <v>12349500</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>38975400</v>
+        <v>39945600</v>
       </c>
       <c r="E60" s="3">
-        <v>49051900</v>
+        <v>50272900</v>
       </c>
       <c r="F60" s="3">
-        <v>41934400</v>
+        <v>42978200</v>
       </c>
       <c r="G60" s="3">
-        <v>40131800</v>
+        <v>41130700</v>
       </c>
       <c r="H60" s="3">
-        <v>35569100</v>
+        <v>36454400</v>
       </c>
       <c r="I60" s="3">
-        <v>31495900</v>
+        <v>32279900</v>
       </c>
       <c r="J60" s="3">
-        <v>29574400</v>
+        <v>30310600</v>
       </c>
       <c r="K60" s="3">
         <v>35941700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>137714000</v>
+        <v>141142000</v>
       </c>
       <c r="E61" s="3">
-        <v>139778000</v>
+        <v>143257000</v>
       </c>
       <c r="F61" s="3">
-        <v>136526000</v>
+        <v>139924000</v>
       </c>
       <c r="G61" s="3">
-        <v>130920000</v>
+        <v>134179000</v>
       </c>
       <c r="H61" s="3">
-        <v>75703000</v>
+        <v>77587400</v>
       </c>
       <c r="I61" s="3">
-        <v>55085400</v>
+        <v>56456600</v>
       </c>
       <c r="J61" s="3">
-        <v>52219400</v>
+        <v>53519200</v>
       </c>
       <c r="K61" s="3">
         <v>54002600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>38443700</v>
+        <v>39400700</v>
       </c>
       <c r="E62" s="3">
-        <v>39489900</v>
+        <v>40472800</v>
       </c>
       <c r="F62" s="3">
-        <v>37850400</v>
+        <v>38792600</v>
       </c>
       <c r="G62" s="3">
-        <v>36838900</v>
+        <v>37755900</v>
       </c>
       <c r="H62" s="3">
-        <v>23211300</v>
+        <v>23789000</v>
       </c>
       <c r="I62" s="3">
-        <v>23583000</v>
+        <v>24170000</v>
       </c>
       <c r="J62" s="3">
-        <v>25048500</v>
+        <v>25672000</v>
       </c>
       <c r="K62" s="3">
         <v>29015100</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>252214000</v>
+        <v>258492000</v>
       </c>
       <c r="E66" s="3">
-        <v>270210000</v>
+        <v>276935000</v>
       </c>
       <c r="F66" s="3">
-        <v>258231000</v>
+        <v>264659000</v>
       </c>
       <c r="G66" s="3">
-        <v>247475000</v>
+        <v>253635000</v>
       </c>
       <c r="H66" s="3">
-        <v>150180000</v>
+        <v>153918000</v>
       </c>
       <c r="I66" s="3">
-        <v>123706000</v>
+        <v>126785000</v>
       </c>
       <c r="J66" s="3">
-        <v>119527000</v>
+        <v>122502000</v>
       </c>
       <c r="K66" s="3">
         <v>129310000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-13055900</v>
+        <v>-13380900</v>
       </c>
       <c r="E72" s="3">
-        <v>-28625600</v>
+        <v>-29338100</v>
       </c>
       <c r="F72" s="3">
-        <v>-34779100</v>
+        <v>-35644800</v>
       </c>
       <c r="G72" s="3">
-        <v>-37551100</v>
+        <v>-38485800</v>
       </c>
       <c r="H72" s="3">
-        <v>-37653700</v>
+        <v>-38591000</v>
       </c>
       <c r="I72" s="3">
-        <v>-38068700</v>
+        <v>-39016300</v>
       </c>
       <c r="J72" s="3">
-        <v>-38136800</v>
+        <v>-39086100</v>
       </c>
       <c r="K72" s="3">
         <v>-39116400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>61518800</v>
+        <v>63050100</v>
       </c>
       <c r="E76" s="3">
-        <v>52476600</v>
+        <v>53782800</v>
       </c>
       <c r="F76" s="3">
-        <v>46123200</v>
+        <v>47271300</v>
       </c>
       <c r="G76" s="3">
-        <v>38820900</v>
+        <v>39787200</v>
       </c>
       <c r="H76" s="3">
-        <v>34265800</v>
+        <v>35118700</v>
       </c>
       <c r="I76" s="3">
-        <v>33401200</v>
+        <v>34232600</v>
       </c>
       <c r="J76" s="3">
-        <v>33213200</v>
+        <v>34039900</v>
       </c>
       <c r="K76" s="3">
         <v>31795900</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>19223500</v>
+        <v>19702000</v>
       </c>
       <c r="E81" s="3">
-        <v>8646700</v>
+        <v>8861900</v>
       </c>
       <c r="F81" s="3">
-        <v>4513000</v>
+        <v>4625300</v>
       </c>
       <c r="G81" s="3">
-        <v>4493600</v>
+        <v>4605400</v>
       </c>
       <c r="H81" s="3">
-        <v>4179100</v>
+        <v>4283100</v>
       </c>
       <c r="I81" s="3">
-        <v>2340800</v>
+        <v>2399100</v>
       </c>
       <c r="J81" s="3">
-        <v>3740300</v>
+        <v>3833400</v>
       </c>
       <c r="K81" s="3">
         <v>2902400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>25909800</v>
+        <v>26554700</v>
       </c>
       <c r="E83" s="3">
-        <v>30072600</v>
+        <v>30821200</v>
       </c>
       <c r="F83" s="3">
-        <v>29388600</v>
+        <v>30120100</v>
       </c>
       <c r="G83" s="3">
-        <v>26886700</v>
+        <v>27556000</v>
       </c>
       <c r="H83" s="3">
-        <v>18743700</v>
+        <v>19210200</v>
       </c>
       <c r="I83" s="3">
-        <v>14952600</v>
+        <v>15324800</v>
       </c>
       <c r="J83" s="3">
-        <v>15763100</v>
+        <v>16155500</v>
       </c>
       <c r="K83" s="3">
         <v>14517300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>40333900</v>
+        <v>41337800</v>
       </c>
       <c r="E89" s="3">
-        <v>38690100</v>
+        <v>39653200</v>
       </c>
       <c r="F89" s="3">
-        <v>34840700</v>
+        <v>35707900</v>
       </c>
       <c r="G89" s="3">
-        <v>25581200</v>
+        <v>26218000</v>
       </c>
       <c r="H89" s="3">
-        <v>24936100</v>
+        <v>25556800</v>
       </c>
       <c r="I89" s="3">
-        <v>19387800</v>
+        <v>19870300</v>
       </c>
       <c r="J89" s="3">
-        <v>18587000</v>
+        <v>19049600</v>
       </c>
       <c r="K89" s="3">
         <v>16850100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13299100</v>
+        <v>-13630100</v>
       </c>
       <c r="E91" s="3">
-        <v>-17899600</v>
+        <v>-18345200</v>
       </c>
       <c r="F91" s="3">
-        <v>-14714800</v>
+        <v>-15081100</v>
       </c>
       <c r="G91" s="3">
-        <v>-13982100</v>
+        <v>-14330100</v>
       </c>
       <c r="H91" s="3">
-        <v>-10787500</v>
+        <v>-11056100</v>
       </c>
       <c r="I91" s="3">
-        <v>-9876500</v>
+        <v>-10122400</v>
       </c>
       <c r="J91" s="3">
-        <v>-9887300</v>
+        <v>-10133400</v>
       </c>
       <c r="K91" s="3">
         <v>-8720100</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-11037200</v>
+        <v>-11311900</v>
       </c>
       <c r="E94" s="3">
-        <v>-24106100</v>
+        <v>-24706100</v>
       </c>
       <c r="F94" s="3">
-        <v>-29614400</v>
+        <v>-30351600</v>
       </c>
       <c r="G94" s="3">
-        <v>-24476800</v>
+        <v>-25086000</v>
       </c>
       <c r="H94" s="3">
-        <v>-15378400</v>
+        <v>-15761100</v>
       </c>
       <c r="I94" s="3">
-        <v>-15450800</v>
+        <v>-15835400</v>
       </c>
       <c r="J94" s="3">
-        <v>-18170900</v>
+        <v>-18623200</v>
       </c>
       <c r="K94" s="3">
         <v>-14764700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4352000</v>
+        <v>-4460300</v>
       </c>
       <c r="E96" s="3">
-        <v>-3658200</v>
+        <v>-3749200</v>
       </c>
       <c r="F96" s="3">
-        <v>-3398800</v>
+        <v>-3483400</v>
       </c>
       <c r="G96" s="3">
-        <v>-3314500</v>
+        <v>-3397000</v>
       </c>
       <c r="H96" s="3">
-        <v>-3848400</v>
+        <v>-3944200</v>
       </c>
       <c r="I96" s="3">
-        <v>-3330700</v>
+        <v>-3413600</v>
       </c>
       <c r="J96" s="3">
-        <v>-1684800</v>
+        <v>-1726700</v>
       </c>
       <c r="K96" s="3">
         <v>-1731700</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-27594600</v>
+        <v>-28281500</v>
       </c>
       <c r="E100" s="3">
-        <v>-16683800</v>
+        <v>-17099100</v>
       </c>
       <c r="F100" s="3">
-        <v>-11648900</v>
+        <v>-11938800</v>
       </c>
       <c r="G100" s="3">
-        <v>8171200</v>
+        <v>8374600</v>
       </c>
       <c r="H100" s="3">
-        <v>-7717300</v>
+        <v>-7909400</v>
       </c>
       <c r="I100" s="3">
-        <v>-3522000</v>
+        <v>-3609700</v>
       </c>
       <c r="J100" s="3">
-        <v>-4964700</v>
+        <v>-5088300</v>
       </c>
       <c r="K100" s="3">
         <v>-1434400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-73500</v>
+        <v>-75300</v>
       </c>
       <c r="E101" s="3">
-        <v>100500</v>
+        <v>103000</v>
       </c>
       <c r="F101" s="3">
-        <v>670000</v>
+        <v>686700</v>
       </c>
       <c r="G101" s="3">
-        <v>-1119600</v>
+        <v>-1147500</v>
       </c>
       <c r="H101" s="3">
-        <v>11900</v>
+        <v>12200</v>
       </c>
       <c r="I101" s="3">
-        <v>-18400</v>
+        <v>-18800</v>
       </c>
       <c r="J101" s="3">
-        <v>-244200</v>
+        <v>-250300</v>
       </c>
       <c r="K101" s="3">
         <v>271300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1628600</v>
+        <v>1669200</v>
       </c>
       <c r="E102" s="3">
-        <v>-1999300</v>
+        <v>-2049100</v>
       </c>
       <c r="F102" s="3">
-        <v>-5752600</v>
+        <v>-5895800</v>
       </c>
       <c r="G102" s="3">
-        <v>8156000</v>
+        <v>8359100</v>
       </c>
       <c r="H102" s="3">
-        <v>1852300</v>
+        <v>1898400</v>
       </c>
       <c r="I102" s="3">
-        <v>396600</v>
+        <v>406500</v>
       </c>
       <c r="J102" s="3">
-        <v>-4792900</v>
+        <v>-4912200</v>
       </c>
       <c r="K102" s="3">
         <v>922300</v>

--- a/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>DTEGY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>124018000</v>
+        <v>126818800</v>
       </c>
       <c r="E8" s="3">
-        <v>126484600</v>
+        <v>125119200</v>
       </c>
       <c r="F8" s="3">
-        <v>119188800</v>
+        <v>125636300</v>
       </c>
       <c r="G8" s="3">
-        <v>111866500</v>
+        <v>125647700</v>
       </c>
       <c r="H8" s="3">
-        <v>89196100</v>
+        <v>93114100</v>
       </c>
       <c r="I8" s="3">
-        <v>83796600</v>
+        <v>89441300</v>
       </c>
       <c r="J8" s="3">
-        <v>83011300</v>
+        <v>92785800</v>
       </c>
       <c r="K8" s="3">
         <v>79308100</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>49272700</v>
+        <v>71807200</v>
       </c>
       <c r="E9" s="3">
-        <v>55433200</v>
+        <v>76010500</v>
       </c>
       <c r="F9" s="3">
-        <v>51597500</v>
+        <v>76415300</v>
       </c>
       <c r="G9" s="3">
-        <v>46425100</v>
+        <v>75833600</v>
       </c>
       <c r="H9" s="3">
-        <v>38222200</v>
+        <v>59279500</v>
       </c>
       <c r="I9" s="3">
-        <v>39586700</v>
+        <v>61308700</v>
       </c>
       <c r="J9" s="3">
-        <v>39705200</v>
+        <v>63906100</v>
       </c>
       <c r="K9" s="3">
         <v>37957600</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>74745300</v>
+        <v>55011600</v>
       </c>
       <c r="E10" s="3">
-        <v>71051400</v>
+        <v>49108700</v>
       </c>
       <c r="F10" s="3">
-        <v>67591300</v>
+        <v>49221000</v>
       </c>
       <c r="G10" s="3">
-        <v>65441400</v>
+        <v>49814100</v>
       </c>
       <c r="H10" s="3">
-        <v>50974000</v>
+        <v>33834600</v>
       </c>
       <c r="I10" s="3">
-        <v>44209900</v>
+        <v>28132600</v>
       </c>
       <c r="J10" s="3">
-        <v>43306100</v>
+        <v>28879700</v>
       </c>
       <c r="K10" s="3">
         <v>41350400</v>
@@ -879,11 +879,11 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>32100</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1252700</v>
+        <v>1485600</v>
       </c>
       <c r="E14" s="3">
-        <v>-566000</v>
+        <v>-824000</v>
       </c>
       <c r="F14" s="3">
-        <v>931500</v>
+        <v>1187300</v>
       </c>
       <c r="G14" s="3">
-        <v>196000</v>
+        <v>1009200</v>
       </c>
       <c r="H14" s="3">
-        <v>814100</v>
+        <v>1366800</v>
       </c>
       <c r="I14" s="3">
-        <v>1333600</v>
+        <v>2173100</v>
       </c>
       <c r="J14" s="3">
-        <v>543800</v>
+        <v>-76800</v>
       </c>
       <c r="K14" s="3">
         <v>732400</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>26309900</v>
+        <v>26251800</v>
       </c>
       <c r="E15" s="3">
-        <v>29540800</v>
+        <v>28278300</v>
       </c>
       <c r="F15" s="3">
-        <v>30124500</v>
+        <v>30482200</v>
       </c>
       <c r="G15" s="3">
-        <v>27724300</v>
+        <v>30072200</v>
       </c>
       <c r="H15" s="3">
-        <v>19128300</v>
+        <v>19380500</v>
       </c>
       <c r="I15" s="3">
-        <v>14525100</v>
+        <v>15014900</v>
       </c>
       <c r="J15" s="3">
-        <v>13767500</v>
+        <v>14923200</v>
       </c>
       <c r="K15" s="3">
         <v>13766500</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>100982100</v>
+        <v>102503600</v>
       </c>
       <c r="E17" s="3">
-        <v>109412100</v>
+        <v>109553300</v>
       </c>
       <c r="F17" s="3">
-        <v>105269600</v>
+        <v>110240000</v>
       </c>
       <c r="G17" s="3">
-        <v>97684800</v>
+        <v>109600000</v>
       </c>
       <c r="H17" s="3">
-        <v>78721600</v>
+        <v>81258000</v>
       </c>
       <c r="I17" s="3">
-        <v>74907000</v>
+        <v>78186400</v>
       </c>
       <c r="J17" s="3">
-        <v>72618700</v>
+        <v>81783100</v>
       </c>
       <c r="K17" s="3">
         <v>69365100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>23035900</v>
+        <v>24315200</v>
       </c>
       <c r="E18" s="3">
-        <v>17072500</v>
+        <v>15565900</v>
       </c>
       <c r="F18" s="3">
-        <v>13919200</v>
+        <v>15396300</v>
       </c>
       <c r="G18" s="3">
-        <v>14181700</v>
+        <v>16047700</v>
       </c>
       <c r="H18" s="3">
-        <v>10474600</v>
+        <v>11856100</v>
       </c>
       <c r="I18" s="3">
-        <v>8889600</v>
+        <v>11254900</v>
       </c>
       <c r="J18" s="3">
-        <v>10392600</v>
+        <v>11002600</v>
       </c>
       <c r="K18" s="3">
         <v>9942900</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2483200</v>
+        <v>2505800</v>
       </c>
       <c r="E20" s="3">
-        <v>1375600</v>
+        <v>-453100</v>
       </c>
       <c r="F20" s="3">
-        <v>97500</v>
+        <v>802900</v>
       </c>
       <c r="G20" s="3">
-        <v>566000</v>
+        <v>-753500</v>
       </c>
       <c r="H20" s="3">
-        <v>570400</v>
+        <v>-471300</v>
       </c>
       <c r="I20" s="3">
-        <v>-862800</v>
+        <v>1007600</v>
       </c>
       <c r="J20" s="3">
-        <v>-2073400</v>
+        <v>2635700</v>
       </c>
       <c r="K20" s="3">
         <v>-2063700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>47102500</v>
+        <v>48061200</v>
       </c>
       <c r="E21" s="3">
-        <v>49263800</v>
+        <v>44297300</v>
       </c>
       <c r="F21" s="3">
-        <v>44131300</v>
+        <v>45075600</v>
       </c>
       <c r="G21" s="3">
-        <v>42298700</v>
+        <v>46873400</v>
       </c>
       <c r="H21" s="3">
-        <v>30251700</v>
+        <v>31708000</v>
       </c>
       <c r="I21" s="3">
-        <v>23348800</v>
+        <v>25262200</v>
       </c>
       <c r="J21" s="3">
-        <v>24471700</v>
+        <v>23290100</v>
       </c>
       <c r="K21" s="3">
         <v>22391200</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7296900</v>
+        <v>8056800</v>
       </c>
       <c r="E22" s="3">
-        <v>6290100</v>
+        <v>6069300</v>
       </c>
       <c r="F22" s="3">
-        <v>5567900</v>
+        <v>5717000</v>
       </c>
       <c r="G22" s="3">
-        <v>5137000</v>
+        <v>6166400</v>
       </c>
       <c r="H22" s="3">
-        <v>3003800</v>
+        <v>3202800</v>
       </c>
       <c r="I22" s="3">
-        <v>2319300</v>
+        <v>2491400</v>
       </c>
       <c r="J22" s="3">
-        <v>2787800</v>
+        <v>3072800</v>
       </c>
       <c r="K22" s="3">
         <v>2945800</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>13255800</v>
+        <v>13228700</v>
       </c>
       <c r="E23" s="3">
-        <v>12158100</v>
+        <v>11730300</v>
       </c>
       <c r="F23" s="3">
-        <v>8448800</v>
+        <v>8675100</v>
       </c>
       <c r="G23" s="3">
-        <v>9610600</v>
+        <v>10346200</v>
       </c>
       <c r="H23" s="3">
-        <v>8041200</v>
+        <v>8148400</v>
       </c>
       <c r="I23" s="3">
-        <v>5707500</v>
+        <v>5899900</v>
       </c>
       <c r="J23" s="3">
-        <v>5531400</v>
+        <v>5995400</v>
       </c>
       <c r="K23" s="3">
         <v>4933500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>4067100</v>
+        <v>4058800</v>
       </c>
       <c r="E24" s="3">
-        <v>2145400</v>
+        <v>2070100</v>
       </c>
       <c r="F24" s="3">
-        <v>1918400</v>
+        <v>1969700</v>
       </c>
       <c r="G24" s="3">
-        <v>2136600</v>
+        <v>2272800</v>
       </c>
       <c r="H24" s="3">
-        <v>2207400</v>
+        <v>2236600</v>
       </c>
       <c r="I24" s="3">
-        <v>2020300</v>
+        <v>2088400</v>
       </c>
       <c r="J24" s="3">
-        <v>-618000</v>
+        <v>-670000</v>
       </c>
       <c r="K24" s="3">
         <v>1565700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>9188600</v>
+        <v>9169900</v>
       </c>
       <c r="E26" s="3">
-        <v>10012700</v>
+        <v>9660100</v>
       </c>
       <c r="F26" s="3">
-        <v>6530400</v>
+        <v>6705300</v>
       </c>
       <c r="G26" s="3">
-        <v>7474100</v>
+        <v>8073400</v>
       </c>
       <c r="H26" s="3">
-        <v>5833700</v>
+        <v>5911800</v>
       </c>
       <c r="I26" s="3">
-        <v>3687200</v>
+        <v>3811500</v>
       </c>
       <c r="J26" s="3">
-        <v>6149400</v>
+        <v>6665500</v>
       </c>
       <c r="K26" s="3">
         <v>3367800</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4532300</v>
+        <v>19661800</v>
       </c>
       <c r="E27" s="3">
-        <v>8371200</v>
+        <v>8550800</v>
       </c>
       <c r="F27" s="3">
-        <v>4396100</v>
+        <v>4749200</v>
       </c>
       <c r="G27" s="3">
-        <v>4605400</v>
+        <v>5086200</v>
       </c>
       <c r="H27" s="3">
-        <v>4283100</v>
+        <v>4339600</v>
       </c>
       <c r="I27" s="3">
-        <v>2399100</v>
+        <v>2480000</v>
       </c>
       <c r="J27" s="3">
-        <v>3833400</v>
+        <v>4155900</v>
       </c>
       <c r="K27" s="3">
         <v>2902400</v>
@@ -1590,25 +1590,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>15169700</v>
+        <v>15138700</v>
       </c>
       <c r="E29" s="3">
-        <v>490700</v>
+        <v>473400</v>
       </c>
       <c r="F29" s="3">
-        <v>229300</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>235400</v>
+      </c>
+      <c r="G29" s="3">
+        <v>179800</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2483200</v>
+        <v>-2505800</v>
       </c>
       <c r="E32" s="3">
-        <v>-1375600</v>
+        <v>453100</v>
       </c>
       <c r="F32" s="3">
-        <v>-97500</v>
+        <v>-802900</v>
       </c>
       <c r="G32" s="3">
-        <v>-566000</v>
+        <v>753500</v>
       </c>
       <c r="H32" s="3">
-        <v>-570400</v>
+        <v>471300</v>
       </c>
       <c r="I32" s="3">
-        <v>862800</v>
+        <v>-1007600</v>
       </c>
       <c r="J32" s="3">
-        <v>2073400</v>
+        <v>-2635700</v>
       </c>
       <c r="K32" s="3">
         <v>2063700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>19702000</v>
+        <v>19661800</v>
       </c>
       <c r="E33" s="3">
-        <v>8861900</v>
+        <v>8550800</v>
       </c>
       <c r="F33" s="3">
-        <v>4625300</v>
+        <v>4749200</v>
       </c>
       <c r="G33" s="3">
-        <v>4605400</v>
+        <v>5086200</v>
       </c>
       <c r="H33" s="3">
-        <v>4283100</v>
+        <v>4339600</v>
       </c>
       <c r="I33" s="3">
-        <v>2399100</v>
+        <v>2480000</v>
       </c>
       <c r="J33" s="3">
-        <v>3833400</v>
+        <v>4155900</v>
       </c>
       <c r="K33" s="3">
         <v>2902400</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>19702000</v>
+        <v>19661800</v>
       </c>
       <c r="E35" s="3">
-        <v>8861900</v>
+        <v>8550800</v>
       </c>
       <c r="F35" s="3">
-        <v>4625300</v>
+        <v>4749200</v>
       </c>
       <c r="G35" s="3">
-        <v>4605400</v>
+        <v>5086200</v>
       </c>
       <c r="H35" s="3">
-        <v>4283100</v>
+        <v>4339600</v>
       </c>
       <c r="I35" s="3">
-        <v>2399100</v>
+        <v>2480000</v>
       </c>
       <c r="J35" s="3">
-        <v>3833400</v>
+        <v>4155900</v>
       </c>
       <c r="K35" s="3">
         <v>2902400</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8056700</v>
+        <v>8040200</v>
       </c>
       <c r="E41" s="3">
-        <v>6387500</v>
+        <v>6163300</v>
       </c>
       <c r="F41" s="3">
-        <v>8436600</v>
+        <v>8662600</v>
       </c>
       <c r="G41" s="3">
-        <v>14331200</v>
+        <v>15827500</v>
       </c>
       <c r="H41" s="3">
-        <v>5973300</v>
+        <v>6052100</v>
       </c>
       <c r="I41" s="3">
-        <v>4074900</v>
+        <v>4212300</v>
       </c>
       <c r="J41" s="3">
-        <v>3668400</v>
+        <v>3976900</v>
       </c>
       <c r="K41" s="3">
         <v>8405500</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>121800</v>
+        <v>6600</v>
       </c>
       <c r="E42" s="3">
-        <v>105200</v>
+        <v>5300</v>
       </c>
       <c r="F42" s="3">
-        <v>103000</v>
+        <v>6800</v>
       </c>
       <c r="G42" s="3">
-        <v>103000</v>
+        <v>6100</v>
       </c>
       <c r="H42" s="3">
-        <v>32100</v>
+        <v>31400</v>
       </c>
       <c r="I42" s="3">
-        <v>13300</v>
+        <v>6900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>9600</v>
       </c>
       <c r="K42" s="3">
         <v>2200</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>26070700</v>
+        <v>25584200</v>
       </c>
       <c r="E43" s="3">
-        <v>26589000</v>
+        <v>25655700</v>
       </c>
       <c r="F43" s="3">
-        <v>23728100</v>
+        <v>24362600</v>
       </c>
       <c r="G43" s="3">
-        <v>20960200</v>
+        <v>23149800</v>
       </c>
       <c r="H43" s="3">
-        <v>18098200</v>
+        <v>18251600</v>
       </c>
       <c r="I43" s="3">
-        <v>16535400</v>
+        <v>17093000</v>
       </c>
       <c r="J43" s="3">
-        <v>14370000</v>
+        <v>15578800</v>
       </c>
       <c r="K43" s="3">
         <v>15932100</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2679300</v>
+        <v>2673800</v>
       </c>
       <c r="E44" s="3">
-        <v>2923000</v>
+        <v>2820300</v>
       </c>
       <c r="F44" s="3">
-        <v>3162200</v>
+        <v>3246900</v>
       </c>
       <c r="G44" s="3">
-        <v>2985000</v>
+        <v>3296600</v>
       </c>
       <c r="H44" s="3">
-        <v>1736700</v>
+        <v>1759600</v>
       </c>
       <c r="I44" s="3">
-        <v>1982600</v>
+        <v>2049500</v>
       </c>
       <c r="J44" s="3">
-        <v>2198600</v>
+        <v>2383500</v>
       </c>
       <c r="K44" s="3">
         <v>1767500</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3347200</v>
+        <v>3888600</v>
       </c>
       <c r="E45" s="3">
-        <v>7351100</v>
+        <v>7189300</v>
       </c>
       <c r="F45" s="3">
-        <v>7543900</v>
+        <v>7846000</v>
       </c>
       <c r="G45" s="3">
-        <v>2926300</v>
+        <v>3338200</v>
       </c>
       <c r="H45" s="3">
-        <v>1505200</v>
+        <v>1611500</v>
       </c>
       <c r="I45" s="3">
-        <v>1617100</v>
+        <v>1678500</v>
       </c>
       <c r="J45" s="3">
-        <v>2349200</v>
+        <v>2537200</v>
       </c>
       <c r="K45" s="3">
         <v>2795000</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>40275700</v>
+        <v>40193400</v>
       </c>
       <c r="E46" s="3">
-        <v>43355900</v>
+        <v>41833900</v>
       </c>
       <c r="F46" s="3">
-        <v>42973800</v>
+        <v>44124900</v>
       </c>
       <c r="G46" s="3">
-        <v>41305700</v>
+        <v>45618300</v>
       </c>
       <c r="H46" s="3">
-        <v>27345500</v>
+        <v>27706200</v>
       </c>
       <c r="I46" s="3">
-        <v>24223200</v>
+        <v>25040100</v>
       </c>
       <c r="J46" s="3">
-        <v>22586200</v>
+        <v>24486100</v>
       </c>
       <c r="K46" s="3">
         <v>28902200</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9686000</v>
+        <v>6275000</v>
       </c>
       <c r="E47" s="3">
-        <v>7046600</v>
+        <v>2573500</v>
       </c>
       <c r="F47" s="3">
-        <v>6395300</v>
+        <v>1825300</v>
       </c>
       <c r="G47" s="3">
-        <v>7707800</v>
+        <v>1430000</v>
       </c>
       <c r="H47" s="3">
-        <v>4967600</v>
+        <v>999900</v>
       </c>
       <c r="I47" s="3">
-        <v>2393500</v>
+        <v>1132400</v>
       </c>
       <c r="J47" s="3">
-        <v>7052100</v>
+        <v>5840500</v>
       </c>
       <c r="K47" s="3">
         <v>9342900</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>108399000</v>
+        <v>101263400</v>
       </c>
       <c r="E48" s="3">
-        <v>110158000</v>
+        <v>98890700</v>
       </c>
       <c r="F48" s="3">
-        <v>102505000</v>
+        <v>99215300</v>
       </c>
       <c r="G48" s="3">
-        <v>101098000</v>
+        <v>105870300</v>
       </c>
       <c r="H48" s="3">
-        <v>74813900</v>
+        <v>71131200</v>
       </c>
       <c r="I48" s="3">
-        <v>56078900</v>
+        <v>53204700</v>
       </c>
       <c r="J48" s="3">
-        <v>51922100</v>
+        <v>51945200</v>
       </c>
       <c r="K48" s="3">
         <v>50732400</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>150638000</v>
+        <v>147772700</v>
       </c>
       <c r="E49" s="3">
-        <v>155729000</v>
+        <v>147613600</v>
       </c>
       <c r="F49" s="3">
-        <v>146920000</v>
+        <v>148952600</v>
       </c>
       <c r="G49" s="3">
-        <v>130770000</v>
+        <v>142099100</v>
       </c>
       <c r="H49" s="3">
-        <v>75540500</v>
+        <v>74111800</v>
       </c>
       <c r="I49" s="3">
-        <v>71938600</v>
+        <v>71636100</v>
       </c>
       <c r="J49" s="3">
-        <v>69629300</v>
+        <v>72981500</v>
       </c>
       <c r="K49" s="3">
         <v>65749900</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>12543600</v>
+        <v>13654300</v>
       </c>
       <c r="E52" s="3">
-        <v>14429800</v>
+        <v>15431200</v>
       </c>
       <c r="F52" s="3">
-        <v>13136100</v>
+        <v>13781400</v>
       </c>
       <c r="G52" s="3">
-        <v>12540200</v>
+        <v>16145600</v>
       </c>
       <c r="H52" s="3">
-        <v>6368700</v>
+        <v>11823600</v>
       </c>
       <c r="I52" s="3">
-        <v>6383100</v>
+        <v>9546600</v>
       </c>
       <c r="J52" s="3">
-        <v>5351900</v>
+        <v>9046600</v>
       </c>
       <c r="K52" s="3">
         <v>6378700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>321542000</v>
+        <v>320885400</v>
       </c>
       <c r="E54" s="3">
-        <v>330718000</v>
+        <v>319108700</v>
       </c>
       <c r="F54" s="3">
-        <v>311930000</v>
+        <v>320285500</v>
       </c>
       <c r="G54" s="3">
-        <v>293422000</v>
+        <v>324057500</v>
       </c>
       <c r="H54" s="3">
-        <v>189036000</v>
+        <v>191529600</v>
       </c>
       <c r="I54" s="3">
-        <v>161017000</v>
+        <v>166447200</v>
       </c>
       <c r="J54" s="3">
-        <v>156542000</v>
+        <v>169709400</v>
       </c>
       <c r="K54" s="3">
         <v>161106000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11937700</v>
+        <v>11913300</v>
       </c>
       <c r="E57" s="3">
-        <v>13270200</v>
+        <v>12804300</v>
       </c>
       <c r="F57" s="3">
-        <v>11514600</v>
+        <v>11823000</v>
       </c>
       <c r="G57" s="3">
-        <v>10733800</v>
+        <v>11855700</v>
       </c>
       <c r="H57" s="3">
-        <v>10422500</v>
+        <v>10560000</v>
       </c>
       <c r="I57" s="3">
-        <v>11850200</v>
+        <v>12249800</v>
       </c>
       <c r="J57" s="3">
-        <v>12110500</v>
+        <v>13128000</v>
       </c>
       <c r="K57" s="3">
         <v>11271000</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>14833000</v>
+        <v>16877400</v>
       </c>
       <c r="E58" s="3">
-        <v>19743000</v>
+        <v>20856000</v>
       </c>
       <c r="F58" s="3">
-        <v>17430300</v>
+        <v>19655400</v>
       </c>
       <c r="G58" s="3">
-        <v>17845700</v>
+        <v>21724800</v>
       </c>
       <c r="H58" s="3">
-        <v>14412100</v>
+        <v>17338100</v>
       </c>
       <c r="I58" s="3">
-        <v>9544200</v>
+        <v>12052900</v>
       </c>
       <c r="J58" s="3">
-        <v>7700000</v>
+        <v>10036000</v>
       </c>
       <c r="K58" s="3">
         <v>12321300</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>13174900</v>
+        <v>6161200</v>
       </c>
       <c r="E59" s="3">
-        <v>17259700</v>
+        <v>10043800</v>
       </c>
       <c r="F59" s="3">
-        <v>14033300</v>
+        <v>7426400</v>
       </c>
       <c r="G59" s="3">
-        <v>12551300</v>
+        <v>6329100</v>
       </c>
       <c r="H59" s="3">
-        <v>11619800</v>
+        <v>5064500</v>
       </c>
       <c r="I59" s="3">
-        <v>10885500</v>
+        <v>5005700</v>
       </c>
       <c r="J59" s="3">
-        <v>10500000</v>
+        <v>5654400</v>
       </c>
       <c r="K59" s="3">
         <v>12349500</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>39945600</v>
+        <v>39864000</v>
       </c>
       <c r="E60" s="3">
-        <v>50272900</v>
+        <v>48508100</v>
       </c>
       <c r="F60" s="3">
-        <v>42978200</v>
+        <v>44129400</v>
       </c>
       <c r="G60" s="3">
-        <v>41130700</v>
+        <v>45425100</v>
       </c>
       <c r="H60" s="3">
-        <v>36454400</v>
+        <v>36935200</v>
       </c>
       <c r="I60" s="3">
-        <v>32279900</v>
+        <v>33368400</v>
       </c>
       <c r="J60" s="3">
-        <v>30310600</v>
+        <v>32860200</v>
       </c>
       <c r="K60" s="3">
         <v>35941700</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>141142000</v>
+        <v>143746000</v>
       </c>
       <c r="E61" s="3">
-        <v>143257000</v>
+        <v>141399000</v>
       </c>
       <c r="F61" s="3">
-        <v>139924000</v>
+        <v>144793600</v>
       </c>
       <c r="G61" s="3">
-        <v>134179000</v>
+        <v>149312500</v>
       </c>
       <c r="H61" s="3">
-        <v>77587400</v>
+        <v>79378300</v>
       </c>
       <c r="I61" s="3">
-        <v>56456600</v>
+        <v>59248900</v>
       </c>
       <c r="J61" s="3">
-        <v>53519200</v>
+        <v>59043000</v>
       </c>
       <c r="K61" s="3">
         <v>54002600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>39400700</v>
+        <v>6235200</v>
       </c>
       <c r="E62" s="3">
-        <v>40472800</v>
+        <v>5719800</v>
       </c>
       <c r="F62" s="3">
-        <v>38792600</v>
+        <v>7763000</v>
       </c>
       <c r="G62" s="3">
-        <v>37755900</v>
+        <v>8415900</v>
       </c>
       <c r="H62" s="3">
-        <v>23789000</v>
+        <v>5196900</v>
       </c>
       <c r="I62" s="3">
-        <v>24170000</v>
+        <v>6475800</v>
       </c>
       <c r="J62" s="3">
-        <v>25672000</v>
+        <v>6464900</v>
       </c>
       <c r="K62" s="3">
         <v>29015100</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>258492000</v>
+        <v>220037600</v>
       </c>
       <c r="E66" s="3">
-        <v>276935000</v>
+        <v>225788200</v>
       </c>
       <c r="F66" s="3">
-        <v>264659000</v>
+        <v>227633300</v>
       </c>
       <c r="G66" s="3">
-        <v>253635000</v>
+        <v>235311300</v>
       </c>
       <c r="H66" s="3">
-        <v>153918000</v>
+        <v>139648700</v>
       </c>
       <c r="I66" s="3">
-        <v>126785000</v>
+        <v>116714000</v>
       </c>
       <c r="J66" s="3">
-        <v>122502000</v>
+        <v>118711600</v>
       </c>
       <c r="K66" s="3">
         <v>129310000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-13380900</v>
+        <v>-13353600</v>
       </c>
       <c r="E72" s="3">
-        <v>-29338100</v>
+        <v>-28308200</v>
       </c>
       <c r="F72" s="3">
-        <v>-35644800</v>
+        <v>-36599600</v>
       </c>
       <c r="G72" s="3">
-        <v>-38485800</v>
+        <v>-42504000</v>
       </c>
       <c r="H72" s="3">
-        <v>-38591000</v>
+        <v>-39100000</v>
       </c>
       <c r="I72" s="3">
-        <v>-39016300</v>
+        <v>-40332000</v>
       </c>
       <c r="J72" s="3">
-        <v>-39086100</v>
+        <v>-42373900</v>
       </c>
       <c r="K72" s="3">
         <v>-39116400</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>63050100</v>
+        <v>62921400</v>
       </c>
       <c r="E76" s="3">
-        <v>53782800</v>
+        <v>51894800</v>
       </c>
       <c r="F76" s="3">
-        <v>47271300</v>
+        <v>48537500</v>
       </c>
       <c r="G76" s="3">
-        <v>39787200</v>
+        <v>43941300</v>
       </c>
       <c r="H76" s="3">
-        <v>35118700</v>
+        <v>35581900</v>
       </c>
       <c r="I76" s="3">
-        <v>34232600</v>
+        <v>35387000</v>
       </c>
       <c r="J76" s="3">
-        <v>34039900</v>
+        <v>36904400</v>
       </c>
       <c r="K76" s="3">
         <v>31795900</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>19702000</v>
+        <v>19661800</v>
       </c>
       <c r="E81" s="3">
-        <v>8861900</v>
+        <v>8550800</v>
       </c>
       <c r="F81" s="3">
-        <v>4625300</v>
+        <v>4749200</v>
       </c>
       <c r="G81" s="3">
-        <v>4605400</v>
+        <v>5086200</v>
       </c>
       <c r="H81" s="3">
-        <v>4283100</v>
+        <v>4339600</v>
       </c>
       <c r="I81" s="3">
-        <v>2399100</v>
+        <v>2480000</v>
       </c>
       <c r="J81" s="3">
-        <v>3833400</v>
+        <v>4155900</v>
       </c>
       <c r="K81" s="3">
         <v>2902400</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>26554700</v>
+        <v>19094700</v>
       </c>
       <c r="E83" s="3">
-        <v>30821200</v>
+        <v>21083700</v>
       </c>
       <c r="F83" s="3">
-        <v>30120100</v>
+        <v>23133200</v>
       </c>
       <c r="G83" s="3">
-        <v>27556000</v>
+        <v>22702100</v>
       </c>
       <c r="H83" s="3">
-        <v>19210200</v>
+        <v>14070300</v>
       </c>
       <c r="I83" s="3">
-        <v>15324800</v>
+        <v>10049200</v>
       </c>
       <c r="J83" s="3">
-        <v>16155500</v>
+        <v>9980800</v>
       </c>
       <c r="K83" s="3">
         <v>14517300</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>41337800</v>
+        <v>41226900</v>
       </c>
       <c r="E89" s="3">
-        <v>39653200</v>
+        <v>38280400</v>
       </c>
       <c r="F89" s="3">
-        <v>35707900</v>
+        <v>36587100</v>
       </c>
       <c r="G89" s="3">
-        <v>26218000</v>
+        <v>29043400</v>
       </c>
       <c r="H89" s="3">
-        <v>25556800</v>
+        <v>25893800</v>
       </c>
       <c r="I89" s="3">
-        <v>19870300</v>
+        <v>20549600</v>
       </c>
       <c r="J89" s="3">
-        <v>19049600</v>
+        <v>20648400</v>
       </c>
       <c r="K89" s="3">
         <v>16850100</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13630100</v>
+        <v>-13602300</v>
       </c>
       <c r="E91" s="3">
-        <v>-18345200</v>
+        <v>-17701200</v>
       </c>
       <c r="F91" s="3">
-        <v>-15081100</v>
+        <v>-15485000</v>
       </c>
       <c r="G91" s="3">
-        <v>-14330100</v>
+        <v>-15826300</v>
       </c>
       <c r="H91" s="3">
-        <v>-11056100</v>
+        <v>-11201900</v>
       </c>
       <c r="I91" s="3">
-        <v>-10122400</v>
+        <v>-10463700</v>
       </c>
       <c r="J91" s="3">
-        <v>-10133400</v>
+        <v>-10985800</v>
       </c>
       <c r="K91" s="3">
         <v>-8720100</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-11311900</v>
+        <v>-11288800</v>
       </c>
       <c r="E94" s="3">
-        <v>-24706100</v>
+        <v>-23838800</v>
       </c>
       <c r="F94" s="3">
-        <v>-30351600</v>
+        <v>-31164600</v>
       </c>
       <c r="G94" s="3">
-        <v>-25086000</v>
+        <v>-27705200</v>
       </c>
       <c r="H94" s="3">
-        <v>-15761100</v>
+        <v>-15969000</v>
       </c>
       <c r="I94" s="3">
-        <v>-15835400</v>
+        <v>-16369400</v>
       </c>
       <c r="J94" s="3">
-        <v>-18623200</v>
+        <v>-20189700</v>
       </c>
       <c r="K94" s="3">
         <v>-14764700</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-4460300</v>
+        <v>4451200</v>
       </c>
       <c r="E96" s="3">
-        <v>-3749200</v>
+        <v>3617600</v>
       </c>
       <c r="F96" s="3">
-        <v>-3483400</v>
+        <v>3576700</v>
       </c>
       <c r="G96" s="3">
-        <v>-3397000</v>
+        <v>3751700</v>
       </c>
       <c r="H96" s="3">
-        <v>-3944200</v>
+        <v>3996200</v>
       </c>
       <c r="I96" s="3">
-        <v>-3413600</v>
+        <v>3528700</v>
       </c>
       <c r="J96" s="3">
-        <v>-1726700</v>
+        <v>1872000</v>
       </c>
       <c r="K96" s="3">
         <v>-1731700</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-28281500</v>
+        <v>-28223700</v>
       </c>
       <c r="E100" s="3">
-        <v>-17099100</v>
+        <v>-16498900</v>
       </c>
       <c r="F100" s="3">
-        <v>-11938800</v>
+        <v>-12258600</v>
       </c>
       <c r="G100" s="3">
-        <v>8374600</v>
+        <v>9248900</v>
       </c>
       <c r="H100" s="3">
-        <v>-7909400</v>
+        <v>-8013700</v>
       </c>
       <c r="I100" s="3">
-        <v>-3609700</v>
+        <v>-3731400</v>
       </c>
       <c r="J100" s="3">
-        <v>-5088300</v>
+        <v>-5516300</v>
       </c>
       <c r="K100" s="3">
         <v>-1434400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-75300</v>
+        <v>-75200</v>
       </c>
       <c r="E101" s="3">
-        <v>103000</v>
+        <v>99400</v>
       </c>
       <c r="F101" s="3">
-        <v>686700</v>
+        <v>705100</v>
       </c>
       <c r="G101" s="3">
-        <v>-1147500</v>
+        <v>-1267300</v>
       </c>
       <c r="H101" s="3">
-        <v>12200</v>
+        <v>12300</v>
       </c>
       <c r="I101" s="3">
-        <v>-18800</v>
+        <v>-19500</v>
       </c>
       <c r="J101" s="3">
-        <v>-250300</v>
+        <v>-271400</v>
       </c>
       <c r="K101" s="3">
         <v>271300</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1669200</v>
+        <v>1639200</v>
       </c>
       <c r="E102" s="3">
-        <v>-2049100</v>
+        <v>-1957900</v>
       </c>
       <c r="F102" s="3">
-        <v>-5895800</v>
+        <v>-6131000</v>
       </c>
       <c r="G102" s="3">
-        <v>8359100</v>
+        <v>9319900</v>
       </c>
       <c r="H102" s="3">
-        <v>1898400</v>
+        <v>1923500</v>
       </c>
       <c r="I102" s="3">
-        <v>406500</v>
+        <v>429400</v>
       </c>
       <c r="J102" s="3">
-        <v>-4912200</v>
+        <v>-5329000</v>
       </c>
       <c r="K102" s="3">
         <v>922300</v>

--- a/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>DTEGY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>122613100</v>
+      </c>
+      <c r="E8" s="3">
         <v>126818800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>125119200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>125636300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>125647700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>93114100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>89441300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>92785800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>79308100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>70667900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>70747100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>71929900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>63869600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>68847500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>67791700</v>
+      </c>
+      <c r="E9" s="3">
         <v>71807200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>76010500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>76415300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>75833600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>59279500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>61308700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>63906100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>37957600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>42848100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>43514400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43368200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37613100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39774600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54821400</v>
+      </c>
+      <c r="E10" s="3">
         <v>55011600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>49108700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>49221000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>49814100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>33834600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>28132600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28879700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41350400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>27819900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27232800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>28561700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26256500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>29072900</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,16 +886,17 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E12" s="3">
         <v>27600</v>
-      </c>
-      <c r="E12" s="3">
-        <v>32100</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,83 +979,89 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1485600</v>
+        <v>-1784900</v>
       </c>
       <c r="E14" s="3">
-        <v>-824000</v>
+        <v>1481200</v>
       </c>
       <c r="F14" s="3">
+        <v>-844300</v>
+      </c>
+      <c r="G14" s="3">
         <v>1187300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1009200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1366800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2173100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-76800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>732400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>151100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>134400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>978500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>24202100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3917000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>26251800</v>
+        <v>24750000</v>
       </c>
       <c r="E15" s="3">
-        <v>28278300</v>
+        <v>26256200</v>
       </c>
       <c r="F15" s="3">
+        <v>28298600</v>
+      </c>
+      <c r="G15" s="3">
         <v>30482200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30072200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19380500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>15014900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>14923200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>13766500</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>102503600</v>
+        <v>97352700</v>
       </c>
       <c r="E17" s="3">
-        <v>109553300</v>
+        <v>102508000</v>
       </c>
       <c r="F17" s="3">
+        <v>109573600</v>
+      </c>
+      <c r="G17" s="3">
         <v>110240000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>109600000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>81258000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>78186400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>81783100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>69365100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63493800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>62564600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>66032600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>68219800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62290600</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>24315200</v>
+        <v>25260400</v>
       </c>
       <c r="E18" s="3">
-        <v>15565900</v>
+        <v>24310800</v>
       </c>
       <c r="F18" s="3">
+        <v>15545600</v>
+      </c>
+      <c r="G18" s="3">
         <v>15396300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16047700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11856100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11254900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11002600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9942900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7174200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>8182600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5897300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4350300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6556900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2505800</v>
+        <v>-2610000</v>
       </c>
       <c r="E20" s="3">
-        <v>-453100</v>
+        <v>3280600</v>
       </c>
       <c r="F20" s="3">
+        <v>-996000</v>
+      </c>
+      <c r="G20" s="3">
         <v>802900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-753500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-471300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1007600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2635700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2063700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>366500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-262000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-492800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-80200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>30500</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>48061200</v>
+        <v>52620400</v>
       </c>
       <c r="E21" s="3">
-        <v>44297300</v>
+        <v>47286400</v>
       </c>
       <c r="F21" s="3">
+        <v>44840200</v>
+      </c>
+      <c r="G21" s="3">
         <v>45075600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>46873400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>31708000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25262200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23290100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>22391200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18913100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19887200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18394400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19715700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>23544100</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>8056800</v>
+        <v>6846500</v>
       </c>
       <c r="E22" s="3">
+        <v>7282000</v>
+      </c>
+      <c r="F22" s="3">
         <v>6069300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5717000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6166400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3202800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2491400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3072800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2945800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2663300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3009100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2858900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2568200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3043700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>23768500</v>
+      </c>
+      <c r="E23" s="3">
         <v>13228700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11730300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8675100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>10346200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8148400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5899900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5995400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4933500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4877400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4911600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2545500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6998700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3543700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5488100</v>
+      </c>
+      <c r="E24" s="3">
         <v>4058800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2070100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1969700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2272800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2236600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2088400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-670000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1565700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1302500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1248800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1105300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-1664600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2757300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>18280400</v>
+      </c>
+      <c r="E26" s="3">
         <v>9169900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9660100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6705300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>8073400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5911800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3811500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6665500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3367800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3574800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3662800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1440200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5334100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>786500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11604700</v>
+      </c>
+      <c r="E27" s="3">
         <v>19661800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8550800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4749200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5086200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4339600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2480000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4155900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2902400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3321700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3301500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1112500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5877600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>653800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,39 +1640,42 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>15138700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>473400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>235400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>179800</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2505800</v>
+        <v>2610000</v>
       </c>
       <c r="E32" s="3">
-        <v>453100</v>
+        <v>-3280600</v>
       </c>
       <c r="F32" s="3">
+        <v>996000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-802900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>753500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>471300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1007600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2635700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2063700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-366500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>262000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>492800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>80200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-30500</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11604700</v>
+      </c>
+      <c r="E33" s="3">
         <v>19661800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8550800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4749200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5086200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4339600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2480000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4155900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2902400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3321700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3301500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1112500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5877600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>653800</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11604700</v>
+      </c>
+      <c r="E35" s="3">
         <v>19661800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8550800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4749200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5086200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4339600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2480000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4155900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2902400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3321700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3301500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1112500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5877600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>653800</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8771100</v>
+      </c>
+      <c r="E41" s="3">
         <v>8040200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6163300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8662600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15827500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6052100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4212300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3976900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8405500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7040500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8494200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9533700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4420500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4400600</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E42" s="3">
         <v>6600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>31400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2301400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>5570900</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>25584200</v>
+        <v>23090400</v>
       </c>
       <c r="E43" s="3">
+        <v>24201400</v>
+      </c>
+      <c r="F43" s="3">
         <v>25655700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24362600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>23149800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>18251600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>17093000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>15578800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15932100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12311900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>14870200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12149800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9036500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>15544800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2537500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2673800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2820300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3246900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3296600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1759600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2049500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2383500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1767500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1885400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1697000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1270400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1214400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2544800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3888600</v>
+        <v>4067700</v>
       </c>
       <c r="E45" s="3">
+        <v>5271400</v>
+      </c>
+      <c r="F45" s="3">
         <v>7189300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7846000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3338200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1611500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1678500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2537200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2795000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11611600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8580000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3312300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1735900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2315900</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>38472900</v>
+      </c>
+      <c r="E46" s="3">
         <v>40193400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>41833900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44124900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>45618300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>27706200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25040100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24486100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28902200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32853400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>33644900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>26272100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16490900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>18622500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8441900</v>
+      </c>
+      <c r="E47" s="3">
         <v>6275000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2573500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1825300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1430000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>999900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1132400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5840500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9342900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4442500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3275500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9006200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9472400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10527900</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>96050300</v>
+      </c>
+      <c r="E48" s="3">
         <v>101263400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>98890700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>99215300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>105870300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>71131200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>53204700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>51945200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>50732400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>45565400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44730400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44770200</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>202972000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>152404000</v>
+      </c>
+      <c r="E49" s="3">
         <v>147772700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>147613600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>148952600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>142099100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>74111800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>71636100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>72981500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>65749900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>58211100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>58222000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>54985700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>75914600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>117761000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>13654300</v>
+        <v>12383300</v>
       </c>
       <c r="E52" s="3">
+        <v>13726100</v>
+      </c>
+      <c r="F52" s="3">
         <v>15431200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>13781400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>16145600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>11823600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9546600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9046600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6378700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5841000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6187500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6294400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7088700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9460900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>315699300</v>
+      </c>
+      <c r="E54" s="3">
         <v>320885400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>319108700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>320285500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>324057500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>191529600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>166447200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>169709400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>161106000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>146914000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146060000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>141329000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>118520000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>143787000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9694600</v>
+      </c>
+      <c r="E57" s="3">
         <v>11913300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12804300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11823000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11855700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>10560000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12249800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13128000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11271000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11266600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10874400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8649700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7043700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15077600</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>16074100</v>
+      </c>
+      <c r="E58" s="3">
         <v>16877400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20856000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>19655400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>21724800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>17338100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12052900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10036000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12321300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12831500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9269900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7060000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>8352500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23990300</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6100000</v>
+      </c>
+      <c r="E59" s="3">
         <v>6161200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10043800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7426400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6329100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5064500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5005700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5654400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12349500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10147800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11694100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11200000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17387900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17246800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>36424100</v>
+      </c>
+      <c r="E60" s="3">
         <v>39864000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>48508100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>44129400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>45425100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36935200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>33368400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32860200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35941700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>34245800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>31838400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26909700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25248500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28423800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>141746600</v>
+      </c>
+      <c r="E61" s="3">
         <v>143746000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>141399000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>144793600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>149312500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>79378300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>59248900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59043000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>54002600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48172600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>49657800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>50550200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>37940300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>44721000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5347300</v>
+      </c>
+      <c r="E62" s="3">
         <v>6235200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5719800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7763000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8415900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5196900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6475800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6464900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29015100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>25551600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26100300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>25514900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28140600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30198600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>213577000</v>
+      </c>
+      <c r="E66" s="3">
         <v>220037600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>225788200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>227633300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>235311300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>139648700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>116714000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>118711600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>129310000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>116902000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>117340000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>112765000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>90051400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>102232000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-5953000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-13353600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-28308200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36599600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-42504000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39100000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-40332000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-42373900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39116400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36457900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-41617500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-43669700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-75680700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-58425200</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>65530600</v>
+      </c>
+      <c r="E76" s="3">
         <v>62921400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>51894800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>48537500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>43941300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35581900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35387000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36904400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>31795900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>30011500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28720900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28564100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28468900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41555200</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11604700</v>
+      </c>
+      <c r="E81" s="3">
         <v>19661800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8550800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4749200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5086200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4339600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2480000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4155900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2902400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3321700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3301500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1112500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5877600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>653800</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>17882800</v>
+      </c>
+      <c r="E83" s="3">
         <v>19094700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21083700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>23133200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22702100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>14070300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10049200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9980800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14517300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11596300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11939100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>13043400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>24108800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16945100</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41281700</v>
+      </c>
+      <c r="E89" s="3">
         <v>41226900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>38280400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>36587100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29043400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25893800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>20549600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20648400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16850100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15310000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15158200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15532700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14907500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19032200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11593300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13602300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-17701200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15485000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15826300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11201900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10463700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10985800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8720100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8336900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8113700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7859000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6171900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9867000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19567200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11288800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23838800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-31164600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27705200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15969000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16369400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20189700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14764700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-15327300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12150200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11837600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7324800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10887100</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>5789400</v>
+      </c>
+      <c r="E96" s="3">
         <v>4451200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3617600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3576700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3751700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3996200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3528700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1872000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1731700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1282100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1456500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2683100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-3733200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-4133000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20998000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-28223700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-16498900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12258600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9248900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8013700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-3731400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-5516300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1434400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-894200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3877300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1222500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7247900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6993600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>523900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-75200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>99400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>705100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1267300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>12300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-19500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-271400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>271300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>272600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>364700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-199800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-30700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-47000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1240300</v>
+      </c>
+      <c r="E102" s="3">
         <v>1639200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1957900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6131000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9319900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1923500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>429400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5329000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>922300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-639000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-504700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>4717800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>304100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1104600</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DTEGY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>DTEGY</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>143026900</v>
+      </c>
+      <c r="E8" s="3">
         <v>122613100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>126818800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>125119200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>125636300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>125647700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>93114100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>89441300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>92785800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>79308100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>70667900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>70747100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71929900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>63869600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>68847500</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>79322500</v>
+      </c>
+      <c r="E9" s="3">
         <v>67791700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>71807200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>76010500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>76415300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>75833600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>59279500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>61308700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>63906100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37957600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>42848100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43514400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>43368200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>37613100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39774600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>63704400</v>
+      </c>
+      <c r="E10" s="3">
         <v>54821400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>55011600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>49108700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>49221000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>49814100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>33834600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>28132600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>28879700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>41350400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>27819900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>27232800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28561700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>26256500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>29072900</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,16 +899,17 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>21700</v>
+        <v>23500</v>
       </c>
       <c r="E12" s="3">
-        <v>27600</v>
+        <v>22100</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,89 +998,95 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1242200</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1784900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1481200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-844300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1187300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1009200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1366800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2173100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-76800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>732400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>151100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>134400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>978500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>24202100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3917000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>28107300</v>
+      </c>
+      <c r="E15" s="3">
         <v>24750000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26256200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>28298600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>30482200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>30072200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>19380500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15014900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14923200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>13766500</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>112760400</v>
+      </c>
+      <c r="E17" s="3">
         <v>97352700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>102508000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>109573600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>110240000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>109600000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>81258000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>78186400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81783100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>69365100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>63493800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>62564600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>66032600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>68219800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>62290600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30266500</v>
+      </c>
+      <c r="E18" s="3">
         <v>25260400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>24310800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15545600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15396300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16047700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11856100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11254900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11002600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9942900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7174200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>8182600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5897300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4350300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6556900</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-807800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2610000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3280600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-996000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>802900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-753500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-471300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1007600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2635700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2063700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>366500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-262000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-492800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-80200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>30500</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>59181600</v>
+      </c>
+      <c r="E21" s="3">
         <v>52620400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47286400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>44840200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>45075600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>46873400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>31708000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>25262200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23290100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22391200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18913100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19887200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18394400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19715700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>23544100</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7657600</v>
+      </c>
+      <c r="E22" s="3">
         <v>6846500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>7282000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6069300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5717000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>6166400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3202800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2491400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3072800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2945800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2663300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3009100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2858900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2568200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3043700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22894200</v>
+      </c>
+      <c r="E23" s="3">
         <v>23768500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13228700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11730300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8675100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10346200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8148400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5899900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5995400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4933500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4877400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4911600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2545500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-6998700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3543700</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5369300</v>
+      </c>
+      <c r="E24" s="3">
         <v>5488100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4058800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2070100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1969700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2272800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2236600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2088400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-670000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1565700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1302500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1248800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1105300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1664600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2757300</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17525000</v>
+      </c>
+      <c r="E26" s="3">
         <v>18280400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9169900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9660100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6705300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8073400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5911800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3811500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6665500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3367800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3574800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3662800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1440200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5334100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>786500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11282100</v>
+      </c>
+      <c r="E27" s="3">
         <v>11604700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19661800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8550800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4749200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5086200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4339600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2480000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4155900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2902400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3321700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3301500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1112500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5877600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>653800</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1653,32 +1713,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>15138700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>473400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>235400</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>179800</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
       <c r="J29" s="3">
         <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>807800</v>
+      </c>
+      <c r="E32" s="3">
         <v>2610000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3280600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>996000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-802900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>753500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>471300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1007600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2635700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2063700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-366500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>262000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>492800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>80200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-30500</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11282100</v>
+      </c>
+      <c r="E33" s="3">
         <v>11604700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19661800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8550800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4749200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5086200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4339600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2480000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4155900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2902400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3321700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3301500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1112500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5877600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>653800</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11282100</v>
+      </c>
+      <c r="E35" s="3">
         <v>11604700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19661800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8550800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4749200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5086200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4339600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2480000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4155900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2902400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3321700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3301500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1112500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5877600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>653800</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9179300</v>
+      </c>
+      <c r="E41" s="3">
         <v>8771100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8040200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6163300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8662600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>15827500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6052100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4212300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3976900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8405500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7040500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8494200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9533700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4420500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4400600</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E42" s="3">
         <v>6200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>31400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>6900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2301400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5570900</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27402800</v>
+      </c>
+      <c r="E43" s="3">
         <v>23090400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24201400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25655700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24362600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>23149800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>18251600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>17093000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>15578800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>15932100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12311900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14870200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12149800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9036500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>15544800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3365000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2537500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2673800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2820300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3246900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3296600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1759600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2049500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2383500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1767500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1885400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1697000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1270400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1214400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2544800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8387900</v>
+      </c>
+      <c r="E45" s="3">
         <v>4067700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5271400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7189300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7846000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3338200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1611500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1678500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2537200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2795000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11611600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8580000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3312300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1735900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2315900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>48346800</v>
+      </c>
+      <c r="E46" s="3">
         <v>38472900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40193400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>41833900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>44124900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>45618300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>27706200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>25040100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>24486100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28902200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32853400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>33644900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>26272100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16490900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>18622500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14233900</v>
+      </c>
+      <c r="E47" s="3">
         <v>8441900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6275000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2573500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1825300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1430000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>999900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1132400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5840500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9342900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4442500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3275500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9006200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9472400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10527900</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>103450700</v>
+      </c>
+      <c r="E48" s="3">
         <v>96050300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>101263400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>98890700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>99215300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>105870300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>71131200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>53204700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51945200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50732400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>45565400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>44730400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>44770200</v>
       </c>
-      <c r="P48" s="3" t="s">
+      <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>202972000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>154943100</v>
+      </c>
+      <c r="E49" s="3">
         <v>152404000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>147772700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>147613600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>148952600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>142099100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>74111800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>71636100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>72981500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>65749900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>58211100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>58222000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>54985700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>75914600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>117761000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13487100</v>
+      </c>
+      <c r="E52" s="3">
         <v>12383300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13726100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15431200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13781400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16145600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11823600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9546600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9046600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6378700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5841000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6187500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6294400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7088700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9460900</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>340224300</v>
+      </c>
+      <c r="E54" s="3">
         <v>315699300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>320885400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>319108700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>320285500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>324057500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>191529600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>166447200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>169709400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>161106000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>146914000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>146060000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>141329000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>118520000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>143787000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11150600</v>
+      </c>
+      <c r="E57" s="3">
         <v>9694600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11913300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12804300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11823000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>11855700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10560000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12249800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13128000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11271000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11266600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10874400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8649700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>7043700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15077600</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20044600</v>
+      </c>
+      <c r="E58" s="3">
         <v>16074100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16877400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>20856000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19655400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21724800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>17338100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12052900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10036000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12321300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>12831500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>9269900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7060000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8352500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23990300</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6915600</v>
+      </c>
+      <c r="E59" s="3">
         <v>6100000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6161200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10043800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7426400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6329100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5064500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5005700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5654400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12349500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10147800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11694100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11200000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17387900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17246800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43264100</v>
+      </c>
+      <c r="E60" s="3">
         <v>36424100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39864000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>48508100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44129400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>45425100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36935200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33368400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>32860200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>35941700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34245800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31838400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26909700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25248500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>28423800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>152226100</v>
+      </c>
+      <c r="E61" s="3">
         <v>141746600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>143746000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>141399000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>144793600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>149312500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>79378300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59248900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>59043000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>54002600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48172600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>49657800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50550200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>37940300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>44721000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6334400</v>
+      </c>
+      <c r="E62" s="3">
         <v>5347300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6235200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5719800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7763000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8415900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5196900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6475800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6464900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29015100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>25551600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26100300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>25514900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>28140600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30198600</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>231932600</v>
+      </c>
+      <c r="E66" s="3">
         <v>213577000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>220037600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>225788200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>227633300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>235311300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>139648700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>116714000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>118711600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>129310000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>116902000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>117340000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>112765000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>90051400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>102232000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1922000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-5953000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-13353600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28308200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36599600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-42504000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39100000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-40332000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-42373900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39116400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36457900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-41617500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-43669700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-75680700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-58425200</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>72996400</v>
+      </c>
+      <c r="E76" s="3">
         <v>65530600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>62921400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>51894800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>48537500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43941300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>35581900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>35387000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>36904400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>31795900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>30011500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>28720900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28564100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28468900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>41555200</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11282100</v>
+      </c>
+      <c r="E81" s="3">
         <v>11604700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19661800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8550800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4749200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5086200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4339600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2480000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4155900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2902400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3321700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3301500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1112500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5877600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>653800</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20135000</v>
+      </c>
+      <c r="E83" s="3">
         <v>17882800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19094700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21083700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>23133200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22702100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>14070300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10049200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9980800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14517300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11596300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11939100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>13043400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>24108800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16945100</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>47701100</v>
+      </c>
+      <c r="E89" s="3">
         <v>41281700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41226900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>38280400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>36587100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29043400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>25893800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20549600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20648400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16850100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>15310000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>15158200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>15532700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14907500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19032200</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14458100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11593300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13602300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17701200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15485000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15826300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11201900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10463700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10985800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8720100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8336900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8113700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7859000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6171900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9867000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-27935900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19567200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11288800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23838800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31164600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27705200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-15969000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16369400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-20189700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-14764700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15327300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12150200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11837600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7324800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10887100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>7559000</v>
+      </c>
+      <c r="E96" s="3">
         <v>5789400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>4451200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3617600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3576700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>3751700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>3996200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>3528700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>1872000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1731700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1282100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1456500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2683100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-3733200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-4133000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19130000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20998000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-28223700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-16498900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12258600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>9248900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8013700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3731400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-5516300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1434400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-894200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3877300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1222500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7247900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6993600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1404300</v>
+      </c>
+      <c r="E101" s="3">
         <v>523900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-75200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>99400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>705100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1267300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-19500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-271400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>271300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>272600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>364700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-199800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-47000</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-769100</v>
+      </c>
+      <c r="E102" s="3">
         <v>1240300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1639200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1957900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6131000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9319900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1923500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>429400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5329000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>922300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-639000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-504700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4717800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>304100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1104600</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
